--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -2490,7 +2490,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2520,11 +2520,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2971,16 +2969,16 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="1" t="s">
@@ -3003,12 +3001,12 @@
       </c>
     </row>
     <row r="21" spans="4:4">
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="4:5">
-      <c r="D22" s="17"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -3075,17 +3073,17 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="17" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -3093,7 +3091,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="17" t="s">
         <v>43</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3101,7 +3099,7 @@
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="19"/>
+      <c r="A36" s="17"/>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" s="1" t="s">
@@ -3109,7 +3107,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="17" t="s">
         <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3135,9 +3133,9 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="1" t="s">
         <v>52</v>
       </c>
@@ -3189,59 +3187,59 @@
       </c>
     </row>
     <row r="53" spans="3:5">
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
     </row>
     <row r="54" spans="3:5">
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
     </row>
     <row r="55" spans="3:5">
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
     </row>
     <row r="58" spans="3:5">
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
     </row>
     <row r="59" spans="3:5">
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
     </row>
     <row r="61" spans="3:5">
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
     </row>
     <row r="63" spans="3:5">
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3666,211 +3664,211 @@
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="17"/>
-      <c r="D12" s="22" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="17"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="3:5">
-      <c r="C14" s="17"/>
-      <c r="D14" s="17" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="17"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="3:5">
-      <c r="C15" s="17"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="3:5">
-      <c r="C16" s="17"/>
-      <c r="D16" s="17" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="17"/>
-      <c r="D17" s="17" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="17"/>
-      <c r="D18" s="17" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="17"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="17"/>
-      <c r="D19" s="17" t="s">
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="3:5">
-      <c r="C20" s="17"/>
-      <c r="D20" s="17" t="s">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="17"/>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="17"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="17"/>
-      <c r="D22" s="17" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="3:5">
-      <c r="C23" s="17"/>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="17"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="3:3">
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="26" spans="3:3">
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="1:8">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="1:8">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="24" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:8">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:8">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:8">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:8">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:8">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="23"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="21"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:8">
       <c r="A34" s="9" t="s">
@@ -3882,9 +3880,9 @@
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="23"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="21"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:8">
       <c r="A35" s="9"/>
@@ -3894,9 +3892,9 @@
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="23"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="21"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:8">
       <c r="A36" s="10" t="s">
@@ -3908,12 +3906,12 @@
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="23"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="21"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:8">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B37" s="10" t="s">
@@ -3924,9 +3922,9 @@
         <v>99</v>
       </c>
       <c r="E37" s="9"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="23"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="21"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:8">
       <c r="A38" s="9"/>
@@ -3938,335 +3936,335 @@
         <v>101</v>
       </c>
       <c r="E38" s="9"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="23"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="21"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:8">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24" t="s">
+      <c r="E39" s="22"/>
+      <c r="F39" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="24"/>
-      <c r="H39" s="23"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="21"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:8">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="23"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="21"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:8">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="23"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="21"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:8">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="23"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="21"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="1:8">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="23"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="21"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="1:8">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="23"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="21"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="1:8">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="23"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="21"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="1:8">
-      <c r="A46" s="24"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="23"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="21"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:8">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="23"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="21"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="23"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="21"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:8">
-      <c r="A49" s="24"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="23"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:8">
-      <c r="A50" s="24"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="23"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="21"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:8">
-      <c r="A51" s="24"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="23"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="21"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:8">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="23"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="21"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:8">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="23"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="21"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:8">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="23"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="21"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:8">
-      <c r="A55" s="24"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="23"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="21"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:8">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="23"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="21"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:8">
-      <c r="A57" s="24"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="23"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="21"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:8">
-      <c r="A58" s="24"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="23"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="21"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:8">
-      <c r="A59" s="24"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="23"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="21"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:8">
-      <c r="A60" s="24"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="23"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="21"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:8">
-      <c r="A61" s="24"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="23"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="21"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:8">
-      <c r="A62" s="24"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="23"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="21"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:8">
-      <c r="A63" s="24"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="23"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="21"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:8">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="23"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="21"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:8">
-      <c r="A65" s="24"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="23"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="21"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:8">
-      <c r="A66" s="24"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="23"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="21"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:8">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="23"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="21"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:8">
-      <c r="A68" s="24"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="23"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="21"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D69" s="17"/>
+      <c r="D69" s="9"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -4274,10 +4272,10 @@
     <row r="70" spans="1:7">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D70" s="17"/>
+      <c r="D70" s="9"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -4285,8 +4283,8 @@
     <row r="71" spans="1:7">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17" t="s">
+      <c r="C71" s="9"/>
+      <c r="D71" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="3"/>
@@ -4294,20 +4292,20 @@
       <c r="G71" s="3"/>
     </row>
     <row r="72" spans="3:4">
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="26" t="s">
+      <c r="A73" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17" t="s">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="27" t="s">
+      <c r="A74" s="25" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4440,7 +4438,7 @@
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:4">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -4448,7 +4446,7 @@
       </c>
     </row>
     <row r="17" ht="14.5" spans="2:5">
-      <c r="B17" s="18"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="1" t="s">
         <v>130</v>
       </c>
@@ -4457,34 +4455,34 @@
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
-      <c r="B18" s="18"/>
+      <c r="B18" s="16"/>
       <c r="D18" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="2:2">
-      <c r="B19" s="18"/>
+      <c r="B19" s="16"/>
     </row>
     <row r="20" ht="14.5" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
-      <c r="B21" s="18"/>
+      <c r="B21" s="16"/>
     </row>
     <row r="22" ht="14.5" spans="2:3">
-      <c r="B22" s="18"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="2:4">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="16" t="s">
         <v>135</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -4492,19 +4490,19 @@
       </c>
     </row>
     <row r="24" ht="14.5" spans="2:3">
-      <c r="B24" s="18"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="2:2">
-      <c r="B25" s="18"/>
+      <c r="B25" s="16"/>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="17" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4648,7 +4646,7 @@
       <c r="A47" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="9" t="s">
         <v>166</v>
       </c>
     </row>
@@ -4775,141 +4773,141 @@
       </c>
     </row>
     <row r="67" spans="3:3">
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="9" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="68" spans="3:4">
-      <c r="C68" s="17"/>
-      <c r="D68" s="17" t="s">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="69" spans="3:5">
-      <c r="C69" s="17"/>
+      <c r="C69" s="9"/>
       <c r="E69" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="70" spans="3:4">
-      <c r="C70" s="17"/>
+      <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="71" spans="3:5">
-      <c r="C71" s="17"/>
+      <c r="C71" s="9"/>
       <c r="E71" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="72" spans="3:4">
-      <c r="C72" s="17"/>
+      <c r="C72" s="9"/>
       <c r="D72" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="73" spans="3:3">
-      <c r="C73" s="17"/>
+      <c r="C73" s="9"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="20"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="20"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="20"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="20"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="20"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="20"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="20"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="20"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
     </row>
     <row r="93" spans="3:4">
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
     </row>
     <row r="94" spans="3:4">
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
     </row>
     <row r="95" spans="3:4">
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
     </row>
     <row r="96" spans="3:4">
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
     </row>
     <row r="97" spans="3:4">
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
     </row>
     <row r="98" spans="4:4">
-      <c r="D98" s="17"/>
+      <c r="D98" s="9"/>
     </row>
     <row r="99" spans="3:4">
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5003,7 +5001,7 @@
     <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="16" customWidth="1"/>
+    <col min="7" max="7" width="4.5" style="15" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.66923076923077" style="1"/>
   </cols>
@@ -5131,118 +5129,118 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F22" s="17"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F23" s="17"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17" t="s">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F24" s="17"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" ht="15.5" spans="1:5">
       <c r="A29"/>
@@ -5306,7 +5304,7 @@
       <c r="D36" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="15">
         <v>5</v>
       </c>
     </row>
@@ -5396,46 +5394,46 @@
       </c>
     </row>
     <row r="3" spans="3:5">
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="3:5">
-      <c r="C4" s="15"/>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="3:5">
-      <c r="C5" s="15"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
-      <c r="C6" s="15"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="15"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="E7" s="15"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="3:5">
-      <c r="C8" s="15"/>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="12" t="s">
@@ -5443,12 +5441,12 @@
       </c>
     </row>
     <row r="10" spans="4:4">
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="10" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="10" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5605,42 +5603,42 @@
       </c>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D35" s="15"/>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="3:4">
-      <c r="C36" s="15"/>
-      <c r="D36" s="15" t="s">
+      <c r="C36" s="10"/>
+      <c r="D36" s="10" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="37" spans="3:4">
-      <c r="C37" s="15"/>
-      <c r="D37" s="15" t="s">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="38" spans="3:4">
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="D38" s="15"/>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
     </row>
     <row r="40" spans="3:4">
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="D40" s="15"/>
+      <c r="D40" s="10"/>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="15"/>
-      <c r="D41" s="15" t="s">
+      <c r="C41" s="10"/>
+      <c r="D41" s="10" t="s">
         <v>301</v>
       </c>
     </row>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="495">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -1344,6 +1344,18 @@
   </si>
   <si>
     <t>http server</t>
+  </si>
+  <si>
+    <t>records</t>
+  </si>
+  <si>
+    <t>Database support includes RedShift, Postgres, MySQL, SQLite, Oracle, and MS-SQL (drivers not included)</t>
+  </si>
+  <si>
+    <t>KDEpy</t>
+  </si>
+  <si>
+    <t>Kernel Density Estimators</t>
   </si>
   <si>
     <t>https://www.quora.com/What-are-the-best-frameworks-for-ETL-processing-using-Python</t>
@@ -2490,7 +2502,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2510,10 +2522,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2907,7 +2922,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -2918,22 +2933,22 @@
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="4:7">
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="7:7">
-      <c r="G6" s="11"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
@@ -2969,16 +2984,16 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="1" t="s">
@@ -3073,17 +3088,17 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -3091,7 +3106,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>43</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3099,7 +3114,7 @@
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="17"/>
+      <c r="A36" s="18"/>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" s="1" t="s">
@@ -3107,7 +3122,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3133,9 +3148,9 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="1" t="s">
         <v>52</v>
       </c>
@@ -3187,59 +3202,59 @@
       </c>
     </row>
     <row r="53" spans="3:5">
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
     </row>
     <row r="54" spans="3:5">
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
     </row>
     <row r="55" spans="3:5">
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
     </row>
     <row r="58" spans="3:5">
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
     </row>
     <row r="59" spans="3:5">
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
     </row>
     <row r="61" spans="3:5">
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
     </row>
     <row r="63" spans="3:5">
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3262,12 +3277,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3275,7 +3290,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -3283,32 +3298,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3316,7 +3331,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3324,32 +3339,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3357,51 +3372,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="5" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -3409,7 +3424,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3417,32 +3432,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="5" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3450,7 +3465,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -3458,32 +3473,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3491,7 +3506,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3499,32 +3514,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="5" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3532,7 +3547,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="4" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -3540,32 +3555,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="5" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -3573,37 +3588,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -3646,7 +3661,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -3674,7 +3689,7 @@
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3687,7 +3702,7 @@
     </row>
     <row r="12" spans="3:5">
       <c r="C12" s="9"/>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="9"/>
@@ -3788,87 +3803,87 @@
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="1:8">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="1:8">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:8">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:8">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:8">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:8">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:8">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="21"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="22"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:8">
       <c r="A34" s="9" t="s">
@@ -3880,9 +3895,9 @@
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="21"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="22"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:8">
       <c r="A35" s="9"/>
@@ -3892,9 +3907,9 @@
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="21"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="22"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:8">
       <c r="A36" s="10" t="s">
@@ -3906,12 +3921,12 @@
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="21"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="22"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:8">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="23" t="s">
         <v>97</v>
       </c>
       <c r="B37" s="10" t="s">
@@ -3922,9 +3937,9 @@
         <v>99</v>
       </c>
       <c r="E37" s="9"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="21"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:8">
       <c r="A38" s="9"/>
@@ -3936,327 +3951,327 @@
         <v>101</v>
       </c>
       <c r="E38" s="9"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="21"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="22"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:8">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="23"/>
+      <c r="F39" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="22"/>
-      <c r="H39" s="21"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="22"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:8">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="21"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="22"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:8">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22" t="s">
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="21"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="22"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:8">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="21"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="22"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="1:8">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22" t="s">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="22"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="1:8">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22" t="s">
+      <c r="A44" s="23"/>
+      <c r="B44" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="21"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="22"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="1:8">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="21"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="22"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="1:8">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="21"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="22"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:8">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="22"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="22"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:8">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="22"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:8">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="22"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:8">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="22"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:8">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="22"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:8">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="22"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:8">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="22"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:8">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="22"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:8">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="22"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:8">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="22"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:8">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="21"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="22"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:8">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="21"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="22"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:8">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="21"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="22"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:8">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="21"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="22"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:8">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="21"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="22"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:8">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="21"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="22"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:8">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="21"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="22"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:8">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="21"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="22"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:8">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="21"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
+      <c r="E66" s="23"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+      <c r="H66" s="22"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:8">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="21"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="22"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:8">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="21"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="22"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3"/>
@@ -4296,7 +4311,7 @@
       <c r="D72" s="9"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="24" t="s">
+      <c r="A73" s="25" t="s">
         <v>113</v>
       </c>
       <c r="B73" s="9"/>
@@ -4305,7 +4320,7 @@
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="26" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4355,7 +4370,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -4369,25 +4384,25 @@
       <c r="C3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="3:7">
       <c r="C4" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="4:7">
       <c r="D6" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
@@ -4438,7 +4453,7 @@
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:4">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -4446,43 +4461,43 @@
       </c>
     </row>
     <row r="17" ht="14.5" spans="2:5">
-      <c r="B17" s="16"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
-      <c r="B18" s="16"/>
+      <c r="B18" s="17"/>
       <c r="D18" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="2:2">
-      <c r="B19" s="16"/>
+      <c r="B19" s="17"/>
     </row>
     <row r="20" ht="14.5" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
-      <c r="B21" s="16"/>
+      <c r="B21" s="17"/>
     </row>
     <row r="22" ht="14.5" spans="2:3">
-      <c r="B22" s="16"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="2:4">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="17" t="s">
         <v>135</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -4490,19 +4505,19 @@
       </c>
     </row>
     <row r="24" ht="14.5" spans="2:3">
-      <c r="B24" s="16"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="2:2">
-      <c r="B25" s="16"/>
+      <c r="B25" s="17"/>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4811,76 +4826,76 @@
       <c r="C73" s="9"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
+      <c r="A74" s="19"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="18"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
+      <c r="A75" s="19"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="18"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
+      <c r="A76" s="19"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
+      <c r="A77" s="19"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="18"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
+      <c r="A78" s="19"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="18"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
+      <c r="A79" s="19"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="18"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
+      <c r="A80" s="19"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="18"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
+      <c r="A81" s="19"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="18"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
+      <c r="A82" s="19"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
     </row>
     <row r="93" spans="3:4">
       <c r="C93" s="9"/>
@@ -4933,7 +4948,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="7:7">
-      <c r="G1" s="11"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -4948,7 +4963,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -5001,7 +5016,7 @@
     <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="15" customWidth="1"/>
+    <col min="7" max="7" width="4.5" style="16" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.66923076923077" style="1"/>
   </cols>
@@ -5024,7 +5039,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -5304,7 +5319,7 @@
       <c r="D36" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="16">
         <v>5</v>
       </c>
     </row>
@@ -5360,36 +5375,36 @@
   <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="25.4153846153846" style="12" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="12" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="12" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="12" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="12" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="12" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="13" customWidth="1"/>
-    <col min="8" max="8" width="4.5" style="12" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="12"/>
+    <col min="1" max="1" width="25.4153846153846" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="11" customWidth="1"/>
+    <col min="3" max="3" width="5.66923076923077" style="11" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="11" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="11" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="11" customWidth="1"/>
+    <col min="7" max="7" width="4.5" style="14" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="11" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="2" spans="2:8">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5409,21 +5424,21 @@
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>256</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>257</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>258</v>
       </c>
       <c r="E7" s="10"/>
@@ -5436,7 +5451,7 @@
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5478,127 +5493,127 @@
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="24" spans="4:4">
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="25" spans="4:4">
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="29" spans="4:4">
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="31" spans="3:3">
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="33" spans="4:5">
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="11" t="s">
         <v>295</v>
       </c>
     </row>
@@ -5643,305 +5658,305 @@
       </c>
     </row>
     <row r="43" spans="3:3">
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="44" spans="4:5">
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="11" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="45" spans="5:5">
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="47" spans="4:4">
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="11" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="48" spans="5:5">
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="11" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="49" spans="5:5">
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="11" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="50" spans="5:5">
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="11" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="52" spans="3:3">
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="53" spans="4:5">
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="54" spans="5:5">
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="55" spans="4:4">
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="11" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="57" spans="2:4">
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="11" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="11" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="59" spans="3:3">
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="60" spans="4:4">
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="61" spans="3:3">
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="11" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="62" spans="2:4">
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="63" spans="2:2">
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="11" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="64" spans="3:3">
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="11" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="65" spans="4:5">
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="11" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="11" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="71" spans="3:3">
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="11" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="72" spans="4:4">
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="11" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="73" spans="4:4">
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="11" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="74" spans="4:4">
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="11" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="75" spans="4:4">
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="11" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="11" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="77" spans="2:4">
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="11" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="11" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="79" spans="4:4">
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="11" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="11" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="81" spans="3:3">
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="11" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="11" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="11" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="84" spans="4:4">
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="11" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="11" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="86" spans="3:3">
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="11" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="11" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="11" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="11" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="92" spans="4:4">
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="11" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="93" spans="4:4">
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="11" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="G94" s="13">
+      <c r="G94" s="14">
         <v>5</v>
       </c>
     </row>
@@ -5981,7 +5996,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -6049,7 +6064,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:D42"/>
+  <dimension ref="A3:D46"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8.66923076923077" style="8"/>
@@ -6382,6 +6397,23 @@
       </c>
       <c r="D42" s="10"/>
     </row>
+    <row r="43" ht="15.5"/>
+    <row r="44" ht="14" spans="2:3">
+      <c r="B44" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="46" ht="14" spans="2:3">
+      <c r="B46" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>439</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="8"/>
+    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="501">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -368,6 +368,21 @@
     <t>for in filter, for in compress, for in groupby</t>
   </si>
   <si>
+    <t>garbage collector</t>
+  </si>
+  <si>
+    <t>gc.collect()</t>
+  </si>
+  <si>
+    <t>import gc</t>
+  </si>
+  <si>
+    <t>datacamp.com/tutorial/python-garbage-collection</t>
+  </si>
+  <si>
+    <t>weakref</t>
+  </si>
+  <si>
     <t>py debuggers</t>
   </si>
   <si>
@@ -462,6 +477,9 @@
   </si>
   <si>
     <t>Basics 804 Set</t>
+  </si>
+  <si>
+    <t>isdigit90</t>
   </si>
   <si>
     <t>bitwise operators</t>
@@ -3277,12 +3295,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3290,7 +3308,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -3298,32 +3316,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3331,7 +3349,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3339,32 +3357,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3372,51 +3390,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="5" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -3424,7 +3442,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3432,32 +3450,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3465,7 +3483,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -3473,32 +3491,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="5" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3506,7 +3524,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="4" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3514,32 +3532,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="5" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3547,7 +3565,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="4" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -3555,32 +3573,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="5" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -3588,37 +3606,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="4" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -4046,7 +4064,9 @@
     <row r="46" ht="16" customHeight="1" spans="1:8">
       <c r="A46" s="23"/>
       <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
+      <c r="C46" s="23" t="s">
+        <v>110</v>
+      </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23"/>
       <c r="F46" s="23"/>
@@ -4055,18 +4075,26 @@
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:8">
       <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
+      <c r="B47" s="23" t="s">
+        <v>111</v>
+      </c>
       <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="23" t="s">
+        <v>112</v>
+      </c>
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
       <c r="G47" s="23"/>
       <c r="H47" s="22"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
-      <c r="A48" s="23"/>
+      <c r="A48" s="23" t="s">
+        <v>113</v>
+      </c>
       <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
+      <c r="C48" s="23" t="s">
+        <v>114</v>
+      </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23"/>
       <c r="F48" s="23"/>
@@ -4277,7 +4305,7 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="3"/>
@@ -4288,7 +4316,7 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="3"/>
@@ -4300,7 +4328,7 @@
       <c r="B71" s="3"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4312,16 +4340,16 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="25" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B73" s="9"/>
       <c r="C73" s="9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4354,7 +4382,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4379,100 +4407,100 @@
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="3:7">
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="4:7">
       <c r="D6" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:4">
       <c r="B16" s="17" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="2:5">
       <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
       <c r="B18" s="17"/>
       <c r="D18" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="2:2">
@@ -4480,11 +4508,11 @@
     </row>
     <row r="20" ht="14.5" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
@@ -4493,21 +4521,21 @@
     <row r="22" ht="14.5" spans="2:3">
       <c r="B22" s="17"/>
       <c r="C22" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="2:4">
       <c r="B23" s="17" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="2:3">
       <c r="B24" s="17"/>
       <c r="C24" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="2:2">
@@ -4515,311 +4543,314 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="C27" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="4:4">
+    <row r="29" spans="2:4">
+      <c r="B29" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="D29" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="4:4">
       <c r="D30" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="4:4">
       <c r="D36" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="5:5">
       <c r="E46" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="3:3">
       <c r="C62" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" s="9" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="3:4">
       <c r="C68" s="9"/>
       <c r="D68" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="3:5">
       <c r="C69" s="9"/>
       <c r="E69" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="3:5">
       <c r="C71" s="9"/>
       <c r="E71" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="3:4">
       <c r="C72" s="9"/>
       <c r="D72" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="3:3">
@@ -4972,29 +5003,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5023,7 +5054,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5048,91 +5079,91 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>34</v>
@@ -5140,14 +5171,14 @@
     </row>
     <row r="16" spans="4:4">
       <c r="D16" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -5158,19 +5189,19 @@
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -5181,33 +5212,33 @@
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -5216,29 +5247,29 @@
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="9" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5247,10 +5278,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="9" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -5301,23 +5332,23 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G36" s="16">
         <v>5</v>
@@ -5325,42 +5356,42 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="5:5">
       <c r="E39" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5388,7 +5419,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="2:8">
@@ -5410,7 +5441,7 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="10" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -5418,66 +5449,66 @@
     <row r="4" spans="3:5">
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
       <c r="D6" s="11" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="3:5">
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="11" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="10" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="10" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="4:4">
@@ -5494,150 +5525,150 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="11" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="11" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="11" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="11" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="11" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="11" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="11" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D38" s="10"/>
     </row>
@@ -5647,314 +5678,314 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" s="11" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="11" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="11" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="11" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="11" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="5:5">
       <c r="E50" s="11" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="11" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" s="11" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="4:5">
       <c r="D53" s="11" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="11" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="11" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="11" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" s="11" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="11" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="11" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="11" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" s="11" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="11" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="4:5">
       <c r="D65" s="11" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="11" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="11" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="11" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="11" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="11" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="11" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="11" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="11" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="11" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="11" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="11" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="11" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="11" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" s="11" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" s="11" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="11" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" s="11" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="11" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="11" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="11" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" s="11" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="11" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G94" s="14">
         <v>5</v>
@@ -6005,39 +6036,39 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6075,37 +6106,37 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="8" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="8" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" ht="14" spans="4:4">
       <c r="D8" s="9" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="8" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" ht="14" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6113,7 +6144,7 @@
     </row>
     <row r="14" ht="14" spans="1:4">
       <c r="A14" s="10" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6122,50 +6153,50 @@
     <row r="15" ht="14" spans="1:4">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D19" s="10"/>
     </row>
@@ -6173,245 +6204,244 @@
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D26" s="10"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D30" s="10"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D34" s="10"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" ht="15.5"/>
     <row r="44" ht="14" spans="2:3">
       <c r="B44" s="11" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
       <c r="B46" s="12" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="1"/>
+    <workbookView windowHeight="17600" tabRatio="698" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="502">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -326,7 +326,7 @@
     <t>Basics 205 Iterators with itertools</t>
   </si>
   <si>
-    <t>repeat, permutations, combinatins</t>
+    <t>repeat, permutations, combinations</t>
   </si>
   <si>
     <t>Self -&gt; basic-ex -&gt; itertools_1</t>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>isdigit90</t>
+  </si>
+  <si>
+    <t>| &amp; - ^</t>
   </si>
   <si>
     <t>bitwise operators</t>
@@ -3295,12 +3298,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3308,7 +3311,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -3316,32 +3319,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3349,7 +3352,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3357,32 +3360,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3390,51 +3393,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -3442,7 +3445,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3450,32 +3453,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3483,7 +3486,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -3491,32 +3494,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3524,7 +3527,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3532,32 +3535,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3565,7 +3568,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -3573,32 +3576,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -3606,37 +3609,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -4583,14 +4586,17 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
+    <row r="32" spans="2:4">
+      <c r="B32" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>132</v>
@@ -4598,12 +4604,12 @@
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="4:4">
@@ -4613,92 +4619,92 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="5:5">
       <c r="E46" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>126</v>
@@ -4711,7 +4717,7 @@
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="4:4">
@@ -4721,29 +4727,29 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="4:4">
@@ -4758,7 +4764,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>132</v>
@@ -4766,33 +4772,33 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="3:3">
       <c r="C62" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="4:4">
@@ -4812,45 +4818,45 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="3:4">
       <c r="C68" s="9"/>
       <c r="D68" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="3:5">
       <c r="C69" s="9"/>
       <c r="E69" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="3:5">
       <c r="C71" s="9"/>
       <c r="E71" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="3:4">
       <c r="C72" s="9"/>
       <c r="D72" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="3:3">
@@ -5003,29 +5009,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -5054,7 +5060,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5079,91 +5085,91 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>34</v>
@@ -5171,14 +5177,14 @@
     </row>
     <row r="16" spans="4:4">
       <c r="D16" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -5189,19 +5195,19 @@
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -5212,33 +5218,33 @@
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -5247,29 +5253,29 @@
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5278,10 +5284,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -5332,23 +5338,23 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G36" s="16">
         <v>5</v>
@@ -5356,42 +5362,42 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="5:5">
       <c r="E39" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5419,7 +5425,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="2:8">
@@ -5441,7 +5447,7 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -5449,66 +5455,66 @@
     <row r="4" spans="3:5">
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
       <c r="D6" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="3:5">
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="4:4">
@@ -5525,150 +5531,150 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D38" s="10"/>
     </row>
@@ -5678,314 +5684,314 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="5:5">
       <c r="E50" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="4:5">
       <c r="D53" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="65" spans="4:5">
       <c r="D65" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G94" s="14">
         <v>5</v>
@@ -6036,39 +6042,39 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -6106,37 +6112,37 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" ht="14" spans="4:4">
       <c r="D8" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" ht="14" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6144,7 +6150,7 @@
     </row>
     <row r="14" ht="14" spans="1:4">
       <c r="A14" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6153,50 +6159,50 @@
     <row r="15" ht="14" spans="1:4">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D19" s="10"/>
     </row>
@@ -6204,244 +6210,244 @@
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>412</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>411</v>
       </c>
       <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D26" s="10"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>415</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>414</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D30" s="10"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D34" s="10"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D42" s="10"/>
     </row>
     <row r="44" ht="14" spans="2:3">
       <c r="B44" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
       <c r="B46" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17600" tabRatio="698" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="13830" windowHeight="17600" tabRatio="698"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="503">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>py version</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/python/python-version-history/</t>
   </si>
   <si>
     <t>compare</t>
@@ -1836,10 +1839,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -2381,16 +2384,16 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2956,15 +2959,18 @@
       </c>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="4:7">
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="13"/>
     </row>
@@ -2973,40 +2979,40 @@
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -3018,120 +3024,120 @@
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="4:5">
       <c r="D22" s="9"/>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="3:6">
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="3:6">
       <c r="C26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -3139,33 +3145,33 @@
     </row>
     <row r="37" spans="3:3">
       <c r="C37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="3:3">
       <c r="C41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="4:4">
       <c r="D42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3173,53 +3179,53 @@
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="4:6">
       <c r="D44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="4:4">
       <c r="D46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="3:5">
@@ -3298,12 +3304,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3311,7 +3317,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -3319,32 +3325,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3352,7 +3358,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3360,32 +3366,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3393,51 +3399,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -3445,7 +3451,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3453,32 +3459,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3486,7 +3492,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -3494,32 +3500,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3527,7 +3533,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3535,32 +3541,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3568,7 +3574,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -3576,32 +3582,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -3609,37 +3615,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -3666,7 +3672,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3691,32 +3697,32 @@
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="3:5">
       <c r="C11" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -3724,87 +3730,87 @@
     <row r="12" spans="3:5">
       <c r="C12" s="9"/>
       <c r="D12" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="3:5">
       <c r="C14" s="9"/>
       <c r="D14" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="3:5">
       <c r="C15" s="9"/>
       <c r="D15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="3:5">
       <c r="C16" s="9"/>
       <c r="D16" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" s="9"/>
       <c r="D17" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="9"/>
       <c r="D18" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="9"/>
       <c r="D19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" s="9"/>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="9"/>
     </row>
     <row r="21" spans="3:5">
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="3:5">
       <c r="C22" s="9"/>
       <c r="D22" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="3:5">
       <c r="C23" s="9"/>
       <c r="D23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="9"/>
     </row>
@@ -3815,17 +3821,17 @@
     </row>
     <row r="25" spans="3:3">
       <c r="C25" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="1:8">
       <c r="A27" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -3839,7 +3845,7 @@
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -3849,7 +3855,7 @@
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:8">
       <c r="A29" s="24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="22"/>
@@ -3860,7 +3866,7 @@
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:8">
       <c r="A30" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
@@ -3872,10 +3878,10 @@
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:8">
       <c r="A31" s="24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="22"/>
@@ -3886,7 +3892,7 @@
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:8">
       <c r="A32" s="23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="23"/>
@@ -3908,11 +3914,11 @@
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:8">
       <c r="A34" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -3923,7 +3929,7 @@
     <row r="35" ht="16" customHeight="1" spans="1:8">
       <c r="A35" s="9"/>
       <c r="B35" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -3934,10 +3940,10 @@
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:8">
       <c r="A36" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -3948,14 +3954,14 @@
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:8">
       <c r="A37" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="23"/>
@@ -3965,11 +3971,11 @@
     <row r="38" ht="16" customHeight="1" spans="1:8">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="23"/>
@@ -3981,11 +3987,11 @@
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G39" s="23"/>
       <c r="H39" s="22"/>
@@ -3994,7 +4000,7 @@
       <c r="A40" s="23"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
@@ -4006,7 +4012,7 @@
       <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
@@ -4016,13 +4022,13 @@
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:8">
       <c r="A42" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
@@ -4033,7 +4039,7 @@
     <row r="43" ht="16" customHeight="1" spans="1:8">
       <c r="A43" s="23"/>
       <c r="B43" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -4045,7 +4051,7 @@
     <row r="44" ht="16" customHeight="1" spans="1:8">
       <c r="A44" s="23"/>
       <c r="B44" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
@@ -4068,7 +4074,7 @@
       <c r="A46" s="23"/>
       <c r="B46" s="23"/>
       <c r="C46" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23"/>
@@ -4079,11 +4085,11 @@
     <row r="47" ht="16" customHeight="1" spans="1:8">
       <c r="A47" s="23"/>
       <c r="B47" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
@@ -4092,11 +4098,11 @@
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
       <c r="A48" s="23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B48" s="23"/>
       <c r="C48" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23"/>
@@ -4308,7 +4314,7 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="3"/>
@@ -4319,7 +4325,7 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="3"/>
@@ -4331,7 +4337,7 @@
       <c r="B71" s="3"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4343,16 +4349,16 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B73" s="9"/>
       <c r="C73" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4385,7 +4391,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4410,100 +4416,100 @@
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="3:7">
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="4:7">
       <c r="D6" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="2:4">
       <c r="B16" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="2:5">
       <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
       <c r="B18" s="17"/>
       <c r="D18" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="2:2">
@@ -4511,11 +4517,11 @@
     </row>
     <row r="20" ht="14.5" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
@@ -4524,21 +4530,21 @@
     <row r="22" ht="14.5" spans="2:3">
       <c r="B22" s="17"/>
       <c r="C22" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="2:4">
       <c r="B23" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="2:3">
       <c r="B24" s="17"/>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="2:2">
@@ -4546,317 +4552,317 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="C27" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="4:4">
       <c r="D30" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="4:4">
       <c r="D36" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="5:5">
       <c r="E46" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="3:3">
       <c r="C62" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="3:4">
       <c r="C68" s="9"/>
       <c r="D68" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="3:5">
       <c r="C69" s="9"/>
       <c r="E69" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="3:5">
       <c r="C71" s="9"/>
       <c r="E71" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="3:4">
       <c r="C72" s="9"/>
       <c r="D72" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="3:3">
@@ -5009,29 +5015,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -5060,7 +5066,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5085,106 +5091,106 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -5195,19 +5201,19 @@
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -5218,33 +5224,33 @@
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -5253,29 +5259,29 @@
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5284,10 +5290,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -5338,23 +5344,23 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G36" s="16">
         <v>5</v>
@@ -5362,42 +5368,42 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="5:5">
       <c r="E39" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5425,7 +5431,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="2:8">
@@ -5447,7 +5453,7 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -5455,66 +5461,66 @@
     <row r="4" spans="3:5">
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
       <c r="D6" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="3:5">
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="4:4">
@@ -5531,150 +5537,150 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D38" s="10"/>
     </row>
@@ -5684,314 +5690,314 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="5:5">
       <c r="E50" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="4:5">
       <c r="D53" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" spans="4:5">
       <c r="D65" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G94" s="14">
         <v>5</v>
@@ -6042,39 +6048,39 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -6112,37 +6118,37 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" ht="14" spans="4:4">
       <c r="D8" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" ht="14" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6150,7 +6156,7 @@
     </row>
     <row r="14" ht="14" spans="1:4">
       <c r="A14" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6159,50 +6165,50 @@
     <row r="15" ht="14" spans="1:4">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D19" s="10"/>
     </row>
@@ -6210,244 +6216,244 @@
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>413</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>412</v>
       </c>
       <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D26" s="10"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>416</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>415</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D30" s="10"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D34" s="10"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D42" s="10"/>
     </row>
     <row r="44" ht="14" spans="2:3">
       <c r="B44" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
       <c r="B46" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13830" windowHeight="17600" tabRatio="698"/>
+    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="516">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -176,6 +176,12 @@
     <t>composition</t>
   </si>
   <si>
+    <t>Adv 504</t>
+  </si>
+  <si>
+    <t>__getattr__ , __setattr__</t>
+  </si>
+  <si>
     <t>inheritance in py</t>
   </si>
   <si>
@@ -440,6 +446,18 @@
     <t>comprehensions</t>
   </si>
   <si>
+    <t>Adv 405 OrderedDict</t>
+  </si>
+  <si>
+    <t>OrderedDict from collections</t>
+  </si>
+  <si>
+    <t>Adv 403</t>
+  </si>
+  <si>
+    <t>defaultDict</t>
+  </si>
+  <si>
     <t>numeric</t>
   </si>
   <si>
@@ -566,6 +584,12 @@
     <t xml:space="preserve">s &gt; n, s &gt; f, </t>
   </si>
   <si>
+    <t>Adv 406</t>
+  </si>
+  <si>
+    <t>deque from collections</t>
+  </si>
+  <si>
     <t>list</t>
   </si>
   <si>
@@ -611,10 +635,25 @@
     <t>insert, append, extend. tolist, getsizeof</t>
   </si>
   <si>
+    <t>Adv 404</t>
+  </si>
+  <si>
+    <t>Counter from collections</t>
+  </si>
+  <si>
     <t>tuple</t>
   </si>
   <si>
     <t>vs set vs list</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>Adv 502</t>
+  </si>
+  <si>
+    <t>unique</t>
   </si>
   <si>
     <t>loop/iteration types</t>
@@ -2915,7 +2954,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="27.3307692307692" style="1" customWidth="1"/>
@@ -3140,63 +3179,64 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="18"/>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="1" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="18" t="s">
+      <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="18"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="18"/>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="3:3">
       <c r="C41" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="1" t="s">
+    <row r="43" spans="3:3">
+      <c r="C43" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="4:6">
+    <row r="44" spans="4:4">
       <c r="D44" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F44" s="1" t="s">
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="4:4">
-      <c r="D45" s="1" t="s">
+    <row r="46" spans="4:6">
+      <c r="D46" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="46" spans="4:4">
-      <c r="D46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3205,43 +3245,38 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="5:5">
-      <c r="E48" s="1" t="s">
+    <row r="48" spans="4:4">
+      <c r="D48" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="3:3">
-      <c r="C49" s="1" t="s">
+    <row r="49" spans="4:4">
+      <c r="D49" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="1" t="s">
+    <row r="50" spans="5:5">
+      <c r="E50" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
+    <row r="52" spans="3:3">
+      <c r="C52" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="1" t="s">
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="3:5">
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-    </row>
-    <row r="54" spans="3:5">
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-    </row>
-    <row r="55" spans="3:5">
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="56" spans="3:5">
       <c r="C56" s="19"/>
@@ -3282,6 +3317,21 @@
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="3:5">
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="3:5">
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="3:5">
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3304,12 +3354,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3317,7 +3367,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -3325,32 +3375,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3358,7 +3408,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3366,32 +3416,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3399,51 +3449,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="5" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="5" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -3451,7 +3501,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3459,32 +3509,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="5" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3492,7 +3542,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -3500,32 +3550,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="5" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3533,7 +3583,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="4" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3541,32 +3591,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="5" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="5" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3574,7 +3624,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="4" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -3582,32 +3632,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="5" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="5" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -3615,37 +3665,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="4" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -3672,7 +3722,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3697,32 +3747,32 @@
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="3:5">
       <c r="C11" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -3730,87 +3780,87 @@
     <row r="12" spans="3:5">
       <c r="C12" s="9"/>
       <c r="D12" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="3:5">
       <c r="C14" s="9"/>
       <c r="D14" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="3:5">
       <c r="C15" s="9"/>
       <c r="D15" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="3:5">
       <c r="C16" s="9"/>
       <c r="D16" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" s="9"/>
       <c r="D17" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="9"/>
       <c r="D18" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="9"/>
       <c r="D19" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E19" s="9"/>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E20" s="9"/>
     </row>
     <row r="21" spans="3:5">
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="3:5">
       <c r="C22" s="9"/>
       <c r="D22" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="3:5">
       <c r="C23" s="9"/>
       <c r="D23" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E23" s="9"/>
     </row>
@@ -3821,17 +3871,17 @@
     </row>
     <row r="25" spans="3:3">
       <c r="C25" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="1:8">
       <c r="A27" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -3845,7 +3895,7 @@
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -3855,7 +3905,7 @@
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:8">
       <c r="A29" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="22"/>
@@ -3866,7 +3916,7 @@
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:8">
       <c r="A30" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
@@ -3878,10 +3928,10 @@
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:8">
       <c r="A31" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="22"/>
@@ -3892,7 +3942,7 @@
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:8">
       <c r="A32" s="23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="22"/>
       <c r="C32" s="23"/>
@@ -3914,11 +3964,11 @@
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:8">
       <c r="A34" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -3929,7 +3979,7 @@
     <row r="35" ht="16" customHeight="1" spans="1:8">
       <c r="A35" s="9"/>
       <c r="B35" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -3940,10 +3990,10 @@
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:8">
       <c r="A36" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -3954,14 +4004,14 @@
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:8">
       <c r="A37" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="23"/>
@@ -3971,11 +4021,11 @@
     <row r="38" ht="16" customHeight="1" spans="1:8">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="23"/>
@@ -3987,11 +4037,11 @@
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G39" s="23"/>
       <c r="H39" s="22"/>
@@ -4000,7 +4050,7 @@
       <c r="A40" s="23"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
@@ -4012,7 +4062,7 @@
       <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
@@ -4022,13 +4072,13 @@
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:8">
       <c r="A42" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
@@ -4039,7 +4089,7 @@
     <row r="43" ht="16" customHeight="1" spans="1:8">
       <c r="A43" s="23"/>
       <c r="B43" s="23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -4051,7 +4101,7 @@
     <row r="44" ht="16" customHeight="1" spans="1:8">
       <c r="A44" s="23"/>
       <c r="B44" s="23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
@@ -4074,7 +4124,7 @@
       <c r="A46" s="23"/>
       <c r="B46" s="23"/>
       <c r="C46" s="23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23"/>
@@ -4085,11 +4135,11 @@
     <row r="47" ht="16" customHeight="1" spans="1:8">
       <c r="A47" s="23"/>
       <c r="B47" s="23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
@@ -4098,11 +4148,11 @@
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
       <c r="A48" s="23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B48" s="23"/>
       <c r="C48" s="23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23"/>
@@ -4314,7 +4364,7 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="3"/>
@@ -4325,7 +4375,7 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="3"/>
@@ -4337,7 +4387,7 @@
       <c r="B71" s="3"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4349,16 +4399,16 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B73" s="9"/>
       <c r="C73" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -4376,7 +4426,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="24.9153846153846" style="1" customWidth="1"/>
@@ -4391,7 +4441,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4416,236 +4466,230 @@
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="3:7">
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="4:7">
       <c r="D6" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3">
-      <c r="C14" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="4:4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" spans="2:4">
-      <c r="B16" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" spans="2:5">
-      <c r="B17" s="17"/>
-      <c r="C17" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
-      <c r="B18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>141</v>
+      </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" spans="2:2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5" spans="2:5">
       <c r="B19" s="17"/>
-    </row>
-    <row r="20" ht="14.5" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="C19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5" spans="2:4">
       <c r="B20" s="17"/>
-      <c r="C20" s="1" t="s">
-        <v>139</v>
+      <c r="D20" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
       <c r="B21" s="17"/>
     </row>
-    <row r="22" ht="14.5" spans="2:3">
+    <row r="22" ht="14.5" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="B22" s="17"/>
       <c r="C22" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" spans="2:4">
-      <c r="B23" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>127</v>
-      </c>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5" spans="2:2">
+      <c r="B23" s="17"/>
     </row>
     <row r="24" ht="14.5" spans="2:3">
       <c r="B24" s="17"/>
       <c r="C24" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" ht="14.5" spans="2:2">
-      <c r="B25" s="17"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5">
-      <c r="C27" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="25" ht="14.5" spans="2:4">
+      <c r="B25" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5" spans="2:3">
+      <c r="B26" s="17"/>
+      <c r="C26" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5" spans="2:2">
+      <c r="B27" s="17"/>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="4:4">
-      <c r="D30" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="4:4">
+    <row r="31" spans="2:4">
+      <c r="B31" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="D31" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>151</v>
-      </c>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
       <c r="D33" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="1" t="s">
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="D35" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="1" t="s">
+    <row r="37" spans="3:3">
+      <c r="C37" s="1" t="s">
         <v>159</v>
       </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
       <c r="B39" s="1" t="s">
         <v>160</v>
       </c>
@@ -4653,319 +4697,370 @@
         <v>161</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
+    <row r="40" spans="2:6">
       <c r="B40" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>163</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
       <c r="B42" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>168</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="45" spans="4:4">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>174</v>
+      </c>
       <c r="D45" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="5:5">
-      <c r="E46" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="1" t="s">
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="1" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5">
+      <c r="E48" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="5:5">
-      <c r="E53" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B54" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3">
+      <c r="C54" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="1" t="s">
-        <v>188</v>
-      </c>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4">
+      <c r="D59" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4">
       <c r="D60" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="62" spans="3:3">
-      <c r="C62" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4">
-      <c r="D63" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="4:4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="D64" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="4:4">
-      <c r="D65" s="1" t="s">
-        <v>130</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="67" spans="3:3">
-      <c r="C67" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4">
-      <c r="C68" s="9"/>
-      <c r="D68" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5">
-      <c r="C69" s="9"/>
-      <c r="E69" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4">
-      <c r="C70" s="9"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3">
+      <c r="C68" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4">
+      <c r="D69" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4">
       <c r="D70" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5">
-      <c r="C71" s="9"/>
-      <c r="E71" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="72" spans="3:4">
-      <c r="C72" s="9"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="D72" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="3:3">
-      <c r="C73" s="9"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="19"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="19"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="19"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="19"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" s="19"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="19"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="19"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="19"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19"/>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="19"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19"/>
-    </row>
-    <row r="93" spans="3:4">
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-    </row>
-    <row r="94" spans="3:4">
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-    </row>
-    <row r="95" spans="3:4">
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-    </row>
-    <row r="96" spans="3:4">
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-    </row>
-    <row r="97" spans="3:4">
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-    </row>
-    <row r="98" spans="4:4">
-      <c r="D98" s="9"/>
-    </row>
-    <row r="99" spans="3:4">
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3">
+      <c r="C74" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
+      <c r="C82" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4">
+      <c r="C83" s="9"/>
+      <c r="D83" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5">
+      <c r="C84" s="9"/>
+      <c r="E84" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4">
+      <c r="C85" s="9"/>
+      <c r="D85" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5">
+      <c r="C86" s="9"/>
+      <c r="E86" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4">
+      <c r="C87" s="9"/>
+      <c r="D87" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="19"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="19"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="19"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="19"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="19"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="19"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="19"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="19"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="19"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="19"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="19"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="19"/>
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="19"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+    </row>
+    <row r="108" spans="3:4">
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+    </row>
+    <row r="109" spans="3:4">
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+    </row>
+    <row r="110" spans="3:4">
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+    </row>
+    <row r="111" spans="3:4">
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+    </row>
+    <row r="112" spans="3:4">
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+    </row>
+    <row r="113" spans="4:4">
+      <c r="D113" s="9"/>
+    </row>
+    <row r="114" spans="3:4">
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5015,29 +5110,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="1" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -5066,7 +5161,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5091,91 +5186,91 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="1" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="1" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>35</v>
@@ -5183,14 +5278,14 @@
     </row>
     <row r="16" spans="4:4">
       <c r="D16" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -5201,19 +5296,19 @@
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -5224,33 +5319,33 @@
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -5259,29 +5354,29 @@
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="9" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5290,10 +5385,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="9" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -5344,23 +5439,23 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="G36" s="16">
         <v>5</v>
@@ -5368,42 +5463,42 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="5:5">
       <c r="E39" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5431,7 +5526,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="11" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="2:8">
@@ -5453,7 +5548,7 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -5461,66 +5556,66 @@
     <row r="4" spans="3:5">
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
       <c r="D6" s="11" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="3:5">
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="11" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="10" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="10" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="4:4">
@@ -5537,150 +5632,150 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="11" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="11" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="11" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="11" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="11" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="11" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="11" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="10" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="10" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="D38" s="10"/>
     </row>
@@ -5690,314 +5785,314 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="10" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" s="11" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="11" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" s="11" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="11" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="5:5">
       <c r="E48" s="11" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="11" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="5:5">
       <c r="E50" s="11" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="11" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" s="11" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="4:5">
       <c r="D53" s="11" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="11" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="11" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="11" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="11" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="11" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" s="11" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="11" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="11" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="11" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" s="11" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="11" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="4:5">
       <c r="D65" s="11" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="11" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="11" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="11" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="11" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="11" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="11" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="11" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="11" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="11" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="11" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="11" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="11" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="11" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" s="11" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="11" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="11" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" s="11" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" s="11" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="11" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" s="11" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="11" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="11" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="11" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" s="11" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="11" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="11" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="G94" s="14">
         <v>5</v>
@@ -6048,39 +6143,39 @@
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="1" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="1" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -6118,37 +6213,37 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="8" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="8" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="8" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" ht="14" spans="4:4">
       <c r="D8" s="9" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="8" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="8" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" ht="14" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6156,7 +6251,7 @@
     </row>
     <row r="14" ht="14" spans="1:4">
       <c r="A14" s="10" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6165,50 +6260,50 @@
     <row r="15" ht="14" spans="1:4">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="D19" s="10"/>
     </row>
@@ -6216,244 +6311,244 @@
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D26" s="10"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="D30" s="10"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="D34" s="10"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D42" s="10"/>
     </row>
     <row r="44" ht="14" spans="2:3">
       <c r="B44" s="11" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
       <c r="B46" s="12" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698"/>
+    <workbookView windowHeight="17600" tabRatio="698" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -1883,7 +1883,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1923,6 +1923,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Bahnschrift"/>
       <charset val="134"/>
@@ -2420,31 +2426,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2453,119 +2456,122 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2585,6 +2591,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2601,20 +2608,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2985,7 +2992,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -2996,7 +3003,7 @@
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="13"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
@@ -3005,16 +3012,16 @@
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="13"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="7:7">
-      <c r="G6" s="13"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
@@ -3050,16 +3057,16 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="1" t="s">
@@ -3154,17 +3161,17 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -3172,7 +3179,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>44</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3180,7 +3187,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -3188,10 +3195,10 @@
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="18"/>
+      <c r="A37" s="19"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="18"/>
+      <c r="A38" s="19"/>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" s="1" t="s">
@@ -3199,7 +3206,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="19" t="s">
         <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -3225,9 +3232,9 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="1" t="s">
         <v>55</v>
       </c>
@@ -3279,59 +3286,59 @@
       </c>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
     </row>
     <row r="58" spans="3:5">
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
     </row>
     <row r="59" spans="3:5">
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
     </row>
     <row r="61" spans="3:5">
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
     </row>
     <row r="63" spans="3:5">
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
     </row>
     <row r="64" spans="3:5">
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
     </row>
     <row r="65" spans="3:5">
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
     </row>
     <row r="66" spans="3:5">
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3738,7 +3745,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -3766,7 +3773,7 @@
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3779,7 +3786,7 @@
     </row>
     <row r="12" spans="3:5">
       <c r="C12" s="9"/>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="22" t="s">
         <v>73</v>
       </c>
       <c r="E12" s="9"/>
@@ -3880,87 +3887,87 @@
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="1:8">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="1:8">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:8">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:8">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:8">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:8">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:8">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="22"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="23"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:8">
       <c r="A34" s="9" t="s">
@@ -3972,9 +3979,9 @@
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="22"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="23"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:8">
       <c r="A35" s="9"/>
@@ -3984,9 +3991,9 @@
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="22"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="23"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:8">
       <c r="A36" s="10" t="s">
@@ -3998,12 +4005,12 @@
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="22"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="23"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:8">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="24" t="s">
         <v>100</v>
       </c>
       <c r="B37" s="10" t="s">
@@ -4014,9 +4021,9 @@
         <v>102</v>
       </c>
       <c r="E37" s="9"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="22"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="23"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:8">
       <c r="A38" s="9"/>
@@ -4028,337 +4035,337 @@
         <v>104</v>
       </c>
       <c r="E38" s="9"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="22"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="23"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:8">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23" t="s">
+      <c r="E39" s="24"/>
+      <c r="F39" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="22"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="23"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:8">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="22"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="23"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:8">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="22"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="23"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:8">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="22"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="23"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="1:8">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23" t="s">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="22"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="23"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="1:8">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23" t="s">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="22"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="23"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="1:8">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="22"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="23"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="1:8">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23" t="s">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="22"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="23"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:8">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23" t="s">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23" t="s">
+      <c r="C47" s="24"/>
+      <c r="D47" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="22"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:8">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23" t="s">
+      <c r="B48" s="24"/>
+      <c r="C48" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="22"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="23"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:8">
-      <c r="A49" s="23"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="22"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="23"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:8">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="22"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="23"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:8">
-      <c r="A51" s="23"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="22"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="23"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:8">
-      <c r="A52" s="23"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="22"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="23"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:8">
-      <c r="A53" s="23"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="22"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="23"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:8">
-      <c r="A54" s="23"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="22"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="23"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:8">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="22"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="23"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:8">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="22"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="23"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:8">
-      <c r="A57" s="23"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="22"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="23"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:8">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="22"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:8">
-      <c r="A59" s="23"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="22"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="23"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:8">
-      <c r="A60" s="23"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="22"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="23"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:8">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="22"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="23"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:8">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="22"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="23"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:8">
-      <c r="A63" s="23"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="22"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="23"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:8">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="22"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="23"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:8">
-      <c r="A65" s="23"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="22"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="23"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:8">
-      <c r="A66" s="23"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="22"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="23"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:8">
-      <c r="A67" s="23"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="22"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="23"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:8">
-      <c r="A68" s="23"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="22"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="23"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3"/>
@@ -4398,7 +4405,7 @@
       <c r="D72" s="9"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="26" t="s">
         <v>121</v>
       </c>
       <c r="B73" s="9"/>
@@ -4407,7 +4414,7 @@
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="26" t="s">
+      <c r="A74" s="27" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4457,7 +4464,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -4471,25 +4478,25 @@
       <c r="C3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="13"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="3:7">
       <c r="C4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="4:7">
       <c r="D5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G5" s="13"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="4:7">
       <c r="D6" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
@@ -4556,7 +4563,7 @@
       </c>
     </row>
     <row r="18" ht="14.5" spans="2:4">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -4564,43 +4571,43 @@
       </c>
     </row>
     <row r="19" ht="14.5" spans="2:5">
-      <c r="B19" s="17"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="2:4">
-      <c r="B20" s="17"/>
+      <c r="B20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="2:2">
-      <c r="B21" s="17"/>
+      <c r="B21" s="18"/>
     </row>
     <row r="22" ht="14.5" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="17"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="2:2">
-      <c r="B23" s="17"/>
+      <c r="B23" s="18"/>
     </row>
     <row r="24" ht="14.5" spans="2:3">
-      <c r="B24" s="17"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="2:4">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>147</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -4608,19 +4615,19 @@
       </c>
     </row>
     <row r="26" ht="14.5" spans="2:3">
-      <c r="B26" s="17"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="2:2">
-      <c r="B27" s="17"/>
+      <c r="B27" s="18"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4964,76 +4971,76 @@
       <c r="C88" s="9"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="19"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="19"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="19"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="19"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="19"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="19"/>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="19"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="19"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
+      <c r="E94" s="20"/>
+      <c r="F94" s="20"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="19"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="19"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="19"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="19"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
+      <c r="A97" s="20"/>
+      <c r="B97" s="20"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
+      <c r="E97" s="20"/>
+      <c r="F97" s="20"/>
     </row>
     <row r="108" spans="3:4">
       <c r="C108" s="9"/>
@@ -5086,7 +5093,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="7:7">
-      <c r="G1" s="13"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -5101,7 +5108,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -5154,7 +5161,7 @@
     <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="16" customWidth="1"/>
+    <col min="7" max="7" width="4.5" style="17" customWidth="1"/>
     <col min="8" max="8" width="4.5" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.66923076923077" style="1"/>
   </cols>
@@ -5177,7 +5184,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -5457,7 +5464,7 @@
       <c r="D36" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <v>5</v>
       </c>
     </row>
@@ -5513,36 +5520,36 @@
   <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="25.4153846153846" style="11" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="11" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="11" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="11" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="11" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="11" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="14" customWidth="1"/>
-    <col min="8" max="8" width="4.5" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="11"/>
+    <col min="1" max="1" width="25.4153846153846" style="12" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="12" customWidth="1"/>
+    <col min="3" max="3" width="5.66923076923077" style="12" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="12" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="12" customWidth="1"/>
+    <col min="7" max="7" width="4.5" style="15" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="2" spans="2:8">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5562,21 +5569,21 @@
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="10"/>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>277</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="3:5">
       <c r="C6" s="10"/>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>278</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="10"/>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E7" s="10"/>
@@ -5589,7 +5596,7 @@
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="4:4">
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>281</v>
       </c>
     </row>
@@ -5631,127 +5638,127 @@
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="24" spans="4:4">
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="25" spans="4:4">
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="29" spans="4:4">
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="31" spans="3:3">
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="33" spans="4:5">
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>316</v>
       </c>
     </row>
@@ -5796,305 +5803,305 @@
       </c>
     </row>
     <row r="43" spans="3:3">
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="44" spans="4:5">
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="45" spans="5:5">
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="47" spans="4:4">
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="12" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="48" spans="5:5">
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="49" spans="5:5">
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="50" spans="5:5">
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="52" spans="3:3">
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="53" spans="4:5">
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="54" spans="5:5">
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="55" spans="4:4">
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="57" spans="2:4">
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="12" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="59" spans="3:3">
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="60" spans="4:4">
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="61" spans="3:3">
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="62" spans="2:4">
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="63" spans="2:2">
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="12" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="64" spans="3:3">
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="65" spans="4:5">
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="12" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="12" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="12" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="71" spans="3:3">
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="72" spans="4:4">
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="12" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="73" spans="4:4">
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="12" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="74" spans="4:4">
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="12" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="75" spans="4:4">
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="77" spans="2:4">
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="79" spans="4:4">
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="12" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="81" spans="3:3">
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="12" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="84" spans="4:4">
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="12" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="86" spans="3:3">
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="12" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="12" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="12" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="92" spans="4:4">
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="12" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="93" spans="4:4">
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="12" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="G94" s="14">
+      <c r="G94" s="15">
         <v>5</v>
       </c>
     </row>
@@ -6134,7 +6141,7 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -6279,7 +6286,7 @@
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="10"/>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>412</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -6289,7 +6296,7 @@
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="10"/>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>414</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6299,7 +6306,7 @@
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="10"/>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>416</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -6309,7 +6316,7 @@
     </row>
     <row r="20" ht="14" spans="1:4">
       <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="10" t="s">
         <v>418</v>
       </c>
@@ -6337,7 +6344,7 @@
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="10"/>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="11" t="s">
         <v>423</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -6367,7 +6374,7 @@
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="10"/>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="11" t="s">
         <v>428</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -6536,18 +6543,18 @@
       <c r="D42" s="10"/>
     </row>
     <row r="44" ht="14" spans="2:3">
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>460</v>
       </c>
     </row>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21290" windowHeight="17600" tabRatio="880" firstSheet="3" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="880" firstSheet="3" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,212 +36,222 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="662">
   <si>
     <t>Most basic things in py</t>
   </si>
   <si>
+    <t>links</t>
+  </si>
+  <si>
+    <t>hints</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>sub-topic</t>
+  </si>
+  <si>
+    <t>py version</t>
+  </si>
+  <si>
+    <t>geeksforgeeks.org/python/python-version-history</t>
+  </si>
+  <si>
+    <t>compare</t>
+  </si>
+  <si>
+    <t>release details</t>
+  </si>
+  <si>
+    <t>w3schools.com/python/python_ref_keywords.asp</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>interpretors in python</t>
+  </si>
+  <si>
+    <t>Global Interpreter Lock (GIL)</t>
+  </si>
+  <si>
+    <t>env tools</t>
+  </si>
+  <si>
+    <t>how to use them</t>
+  </si>
+  <si>
+    <t>operators</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>https://www.w3schools.com/python/python_operators.asp</t>
+  </si>
+  <si>
+    <t>bitwise</t>
+  </si>
+  <si>
+    <t>Python do not have private variable, instead python naming convension use _var This variable should be called directly from object instance.</t>
+  </si>
+  <si>
+    <t>try, catch, except, finally</t>
+  </si>
+  <si>
+    <t>try .. except .. else .. finally</t>
+  </si>
+  <si>
+    <t>else print when when no error in try
+finally always print</t>
+  </si>
+  <si>
+    <t>Conditional Statement</t>
+  </si>
+  <si>
+    <t>if elif else</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>raise</t>
+  </si>
+  <si>
+    <t>TypeError, StopIteration</t>
+  </si>
+  <si>
+    <t>functions / methods</t>
+  </si>
+  <si>
+    <t>default value var</t>
+  </si>
+  <si>
+    <t>*args</t>
+  </si>
+  <si>
+    <t>m1(*aTup)</t>
+  </si>
+  <si>
+    <t>type tuple</t>
+  </si>
+  <si>
+    <t>**args</t>
+  </si>
+  <si>
+    <t>m2(**aDict)</t>
+  </si>
+  <si>
+    <t>type dict</t>
+  </si>
+  <si>
+    <t>Basics 706 Generator</t>
+  </si>
+  <si>
+    <t>generator function</t>
+  </si>
+  <si>
+    <t>yield</t>
+  </si>
+  <si>
+    <t>classes</t>
+  </si>
+  <si>
+    <t>shared among all instances</t>
+  </si>
+  <si>
+    <t>class level vars</t>
+  </si>
+  <si>
+    <t>Using pass:</t>
+  </si>
+  <si>
+    <t>Basics 105 Class method members</t>
+  </si>
+  <si>
+    <t>staticmethod, classmethod</t>
+  </si>
+  <si>
+    <t>Basics 202 Abstract base classes</t>
+  </si>
+  <si>
+    <t>abstractmethod</t>
+  </si>
+  <si>
+    <t>Basics 205 Composition</t>
+  </si>
+  <si>
+    <t>composition</t>
+  </si>
+  <si>
+    <t>Adv 504</t>
+  </si>
+  <si>
+    <t>__getattr__ , __setattr__</t>
+  </si>
+  <si>
+    <t>inheritance in py</t>
+  </si>
+  <si>
+    <t>Basics 203 Multiple inheritance</t>
+  </si>
+  <si>
+    <t>Method Resolution Order</t>
+  </si>
+  <si>
+    <t>__mro__</t>
+  </si>
+  <si>
+    <t>mixin pattern</t>
+  </si>
+  <si>
+    <t>objects</t>
+  </si>
+  <si>
+    <t>__code__</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Ellipisis or ...</t>
+  </si>
+  <si>
+    <t>for slicings</t>
+  </si>
+  <si>
+    <t>NotImplemented</t>
+  </si>
+  <si>
+    <t>Internal Objects</t>
+  </si>
+  <si>
+    <t>contextmanager</t>
+  </si>
+  <si>
+    <t>__enter__ __exit__</t>
+  </si>
+  <si>
+    <t>decorators</t>
+  </si>
+  <si>
+    <t>built-in</t>
+  </si>
+  <si>
+    <t>BASICS-707 Decorator</t>
+  </si>
+  <si>
+    <t>custom decorators pattern</t>
+  </si>
+  <si>
+    <t>Most basic and few extra things in py</t>
+  </si>
+  <si>
     <t>s.no.</t>
   </si>
   <si>
-    <t>hints</t>
-  </si>
-  <si>
-    <t>topic</t>
-  </si>
-  <si>
-    <t>sub-topic</t>
-  </si>
-  <si>
-    <t>py version</t>
-  </si>
-  <si>
-    <t>geeksforgeeks.org/python/python-version-history</t>
-  </si>
-  <si>
-    <t>compare</t>
-  </si>
-  <si>
-    <t>release details</t>
-  </si>
-  <si>
-    <t>w3schools.com/python/python_ref_keywords.asp</t>
-  </si>
-  <si>
-    <t>keywords</t>
-  </si>
-  <si>
-    <t>interpretors in python</t>
-  </si>
-  <si>
-    <t>Global Interpreter Lock (GIL)</t>
-  </si>
-  <si>
-    <t>env tools</t>
-  </si>
-  <si>
-    <t>how to use them</t>
-  </si>
-  <si>
-    <t>operators</t>
-  </si>
-  <si>
-    <t>control</t>
-  </si>
-  <si>
-    <t>https://www.w3schools.com/python/python_operators.asp</t>
-  </si>
-  <si>
-    <t>bitwise</t>
-  </si>
-  <si>
-    <t>Python do not have private variable, instead python naming convension use _var This variable should be called directly from object instance.</t>
-  </si>
-  <si>
-    <t>try, catch, except, finally</t>
-  </si>
-  <si>
-    <t>Conditional Statement</t>
-  </si>
-  <si>
-    <t>if elif else</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>raise</t>
-  </si>
-  <si>
-    <t>TypeError, StopIteration</t>
-  </si>
-  <si>
-    <t>functions / methods</t>
-  </si>
-  <si>
-    <t>default value var</t>
-  </si>
-  <si>
-    <t>*args</t>
-  </si>
-  <si>
-    <t>m1(*aTup)</t>
-  </si>
-  <si>
-    <t>type tuple</t>
-  </si>
-  <si>
-    <t>**args</t>
-  </si>
-  <si>
-    <t>m2(**aDict)</t>
-  </si>
-  <si>
-    <t>type dict</t>
-  </si>
-  <si>
-    <t>Basics 706 Generator</t>
-  </si>
-  <si>
-    <t>generator function</t>
-  </si>
-  <si>
-    <t>yield</t>
-  </si>
-  <si>
-    <t>classes</t>
-  </si>
-  <si>
-    <t>shared among all instances</t>
-  </si>
-  <si>
-    <t>class level vars</t>
-  </si>
-  <si>
-    <t>Using pass:</t>
-  </si>
-  <si>
-    <t>Basics 105 Class method members</t>
-  </si>
-  <si>
-    <t>staticmethod, classmethod</t>
-  </si>
-  <si>
-    <t>Basics 202 Abstract base classes</t>
-  </si>
-  <si>
-    <t>abstractmethod</t>
-  </si>
-  <si>
-    <t>Basics 205 Composition</t>
-  </si>
-  <si>
-    <t>composition</t>
-  </si>
-  <si>
-    <t>Adv 504</t>
-  </si>
-  <si>
-    <t>__getattr__ , __setattr__</t>
-  </si>
-  <si>
-    <t>inheritance in py</t>
-  </si>
-  <si>
-    <t>Basics 203 Multiple inheritance</t>
-  </si>
-  <si>
-    <t>Method Resolution Order</t>
-  </si>
-  <si>
-    <t>__mro__</t>
-  </si>
-  <si>
-    <t>mixin pattern</t>
-  </si>
-  <si>
-    <t>objects</t>
-  </si>
-  <si>
-    <t>__code__</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Ellipisis or ...</t>
-  </si>
-  <si>
-    <t>for slicings</t>
-  </si>
-  <si>
-    <t>NotImplemented</t>
-  </si>
-  <si>
-    <t>Internal Objects</t>
-  </si>
-  <si>
-    <t>contextmanager</t>
-  </si>
-  <si>
-    <t>__enter__ __exit__</t>
-  </si>
-  <si>
-    <t>decorators</t>
-  </si>
-  <si>
-    <t>built-in</t>
-  </si>
-  <si>
-    <t>BASICS-707 Decorator</t>
-  </si>
-  <si>
-    <t>custom decorators pattern</t>
-  </si>
-  <si>
-    <t>Most basic and few extra things in py</t>
-  </si>
-  <si>
     <t>call by reference</t>
   </si>
   <si>
@@ -377,7 +387,107 @@
     <t>operator</t>
   </si>
   <si>
+    <t>Data pretty printer</t>
+  </si>
+  <si>
     <t>pprint</t>
+  </si>
+  <si>
+    <t>import pprint
+pprint.pp(stuff)</t>
+  </si>
+  <si>
+    <t>re</t>
+  </si>
+  <si>
+    <r>
+      <t>import re
+txt = "The rain in Spain"
+x = re.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("^The.*Spain$", txt)
+x = re.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>findall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("ai", txt)
+x.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()  // index first find
+re.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>split</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("\s", txt)   // split on white space
+re.sub("\s", "9", txt) // replace whitespace with 9</t>
+    </r>
+  </si>
+  <si>
+    <t>findall, compile, split, sub, resubin, escape, search</t>
   </si>
   <si>
     <t>for in starmap, for in zip</t>
@@ -574,13 +684,19 @@
     <t>w3schools.com/python/python_ref_dictionary.asp</t>
   </si>
   <si>
-    <t>set, get, update</t>
+    <t xml:space="preserve">set, get, update. pop(keyA), </t>
+  </si>
+  <si>
+    <t>clear</t>
   </si>
   <si>
     <t>loops</t>
   </si>
   <si>
     <t>for k, v in aDict.items():</t>
+  </si>
+  <si>
+    <t>for v in aDict:</t>
   </si>
   <si>
     <t>Adv 203 Dictionaries and sets</t>
@@ -722,10 +838,7 @@
     <t>less used: repr, ascii, chr, ord</t>
   </si>
   <si>
-    <t>reverse string [::-1]</t>
-  </si>
-  <si>
-    <t>startswith</t>
+    <t>reverse string [::-1], startswith</t>
   </si>
   <si>
     <t>Basics 102 Basic string operations</t>
@@ -851,6 +964,24 @@
     <t>insert, append, extend. tolist, getsizeof</t>
   </si>
   <si>
+    <t>from array import array</t>
+  </si>
+  <si>
+    <t>to find memory buffer size</t>
+  </si>
+  <si>
+    <t>from sys import getsizeof</t>
+  </si>
+  <si>
+    <t>geeksforgeeks.org/python/difference-between-list-and-array-in-python/</t>
+  </si>
+  <si>
+    <t>list vs array</t>
+  </si>
+  <si>
+    <t>stackoverflow.com/questions/176011/python-list-vs-array-when-to-use</t>
+  </si>
+  <si>
     <t>Adv 404</t>
   </si>
   <si>
@@ -935,6 +1066,12 @@
     <t>inter-thread communication</t>
   </si>
   <si>
+    <t>tutorialspoint.com/python/python_userdefined_exception.htm</t>
+  </si>
+  <si>
+    <t>User Define Exceptions</t>
+  </si>
+  <si>
     <t>Advance and less used things in py</t>
   </si>
   <si>
@@ -995,15 +1132,31 @@
     <t>with MyContextManager</t>
   </si>
   <si>
+    <t>async def main():
+   async with AsyncContextManager():</t>
+  </si>
+  <si>
     <t>from contextlib import contextmanager</t>
   </si>
   <si>
-    <t>@contextmanager</t>
+    <t>from contextlib import contextmanager
+@contextmanager
+def cm():
+try:
+      yield
+   finally:
+      print("Exiting the context manager method")</t>
   </si>
   <si>
     <t>with open(....) as f:</t>
   </si>
   <si>
+    <t>tutorialspoint.com/python/python_context_managers.htm</t>
+  </si>
+  <si>
+    <t>@asynccontextmanager</t>
+  </si>
+  <si>
     <t>Other iteration methods</t>
   </si>
   <si>
@@ -1100,9 +1253,83 @@
     <t>@unique</t>
   </si>
   <si>
+    <t>tutorialspoint.com/python/python_abstract_base_classes.htm</t>
+  </si>
+  <si>
+    <t>More theoritical Advance concepts</t>
+  </si>
+  <si>
+    <t>Abstract Base Classes</t>
+  </si>
+  <si>
+    <t>Higher Order Fuctions</t>
+  </si>
+  <si>
+    <t>Object Literals</t>
+  </si>
+  <si>
+    <t>Memory Management</t>
+  </si>
+  <si>
+    <t>Metaclasses</t>
+  </si>
+  <si>
+    <t>Metaprogramming with Metaclasses</t>
+  </si>
+  <si>
+    <t>tutorialspoint.com/python/python_metaprogramming_with_metaclasses.htm</t>
+  </si>
+  <si>
+    <t>__prepare__(cls, name, bases, **kwargs):</t>
+  </si>
+  <si>
+    <t>Metaprogramming refers to the practice of writing code that has knowledge of itself and can be manipulated</t>
+  </si>
+  <si>
+    <t>Mocking and stubing</t>
+  </si>
+  <si>
+    <t>Monkey Patching</t>
+  </si>
+  <si>
+    <t>Signal Handling</t>
+  </si>
+  <si>
+    <t>Type Hints</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Humanize Package</t>
+  </si>
+  <si>
+    <t>Context Manager</t>
+  </si>
+  <si>
+    <t>Descritors</t>
+  </si>
+  <si>
+    <t>Diagnosing and Fixing Memory Leaks</t>
+  </si>
+  <si>
+    <t>Immutable Data Structures</t>
+  </si>
+  <si>
     <t>Common modules which can be used anywhere</t>
   </si>
   <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>getting details of any modules for all its member</t>
+  </si>
+  <si>
+    <t>import platform
+x = dir(platform)
+print(x)</t>
+  </si>
+  <si>
     <t>w3schools.com/python/python_ref_exceptions.asp</t>
   </si>
   <si>
@@ -1262,6 +1489,16 @@
     <t>mode</t>
   </si>
   <si>
+    <t>f = open("demofile.txt", "r")
+f.read()</t>
+  </si>
+  <si>
+    <t>with open("demofile.txt", "r") as f: f.readline()</t>
+  </si>
+  <si>
+    <t>for x in f: # here x is each line file</t>
+  </si>
+  <si>
     <t>readline</t>
   </si>
   <si>
@@ -1346,12 +1583,45 @@
     <t>null value</t>
   </si>
   <si>
+    <t>dictionary is default data type returned from loads</t>
+  </si>
+  <si>
     <t>Basics 604 JSON</t>
   </si>
   <si>
     <t>dumps</t>
   </si>
   <si>
+    <t>convert dict to json</t>
+  </si>
+  <si>
+    <t>list to array</t>
+  </si>
+  <si>
+    <t>tuple to array</t>
+  </si>
+  <si>
+    <t>string to string</t>
+  </si>
+  <si>
+    <t>w3schools.com/python/python_examples.asp</t>
+  </si>
+  <si>
+    <t>number, float, bool, None remains same</t>
+  </si>
+  <si>
+    <t>to pritify json output</t>
+  </si>
+  <si>
+    <t>json.dumps(x, indent=4)</t>
+  </si>
+  <si>
+    <t>json.dumps(x, indent=4, separators=(". ", " = "))</t>
+  </si>
+  <si>
+    <t>json.dumps(x, indent=4, sort_keys=True)</t>
+  </si>
+  <si>
     <t>Extr 401 JSON Module</t>
   </si>
   <si>
@@ -1361,9 +1631,6 @@
     <t>dump vs dumps</t>
   </si>
   <si>
-    <t>what js datatype will covert to what via this module</t>
-  </si>
-  <si>
     <t>JSONDecodeError</t>
   </si>
   <si>
@@ -1455,6 +1722,9 @@
   </si>
   <si>
     <t>textwrap</t>
+  </si>
+  <si>
+    <t>type validation</t>
   </si>
   <si>
     <t>fibonacci</t>
@@ -2289,6 +2559,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -2304,12 +2580,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Bahnschrift"/>
@@ -2782,19 +3052,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2803,7 +3073,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2927,7 +3197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2964,41 +3234,65 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3339,39 +3633,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="27.3307692307692" style="6" customWidth="1"/>
     <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="23" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="22" customWidth="1"/>
     <col min="4" max="4" width="3.33076923076923" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="6" customWidth="1"/>
+    <col min="5" max="5" width="3.07692307692308" style="6" customWidth="1"/>
     <col min="6" max="6" width="57.4538461538462" style="6" customWidth="1"/>
     <col min="7" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3397,7 +3697,7 @@
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3407,7 +3707,7 @@
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3417,7 +3717,7 @@
       </c>
     </row>
     <row r="12" spans="3:3">
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3434,289 +3734,235 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6">
-      <c r="A15" s="36" t="s">
+    <row r="15" ht="28" spans="6:6">
+      <c r="F15" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="3:3">
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="23" t="s">
+    <row r="17" spans="4:4">
+      <c r="D17" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="4:4">
-      <c r="D19" s="6" t="s">
+    <row r="18" ht="28" spans="6:6">
+      <c r="F18" s="23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="4:4">
-      <c r="D20" s="6" t="s">
+    <row r="20" spans="3:3">
+      <c r="C20" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="4:4">
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="4:5">
-      <c r="D22" s="14"/>
-      <c r="E22" s="6" t="s">
+    <row r="22" spans="4:4">
+      <c r="D22" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="23" t="s">
+    <row r="23" spans="4:4">
+      <c r="D23" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="4:4">
-      <c r="D24" s="6" t="s">
+    <row r="24" spans="4:5">
+      <c r="D24" s="14"/>
+      <c r="E24" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="6" t="s">
+    <row r="25" spans="3:3">
+      <c r="C25" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="6" t="s">
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="6" t="s">
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="F28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="6" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="3:3">
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="6" t="s">
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="6" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="27" t="s">
+      <c r="D33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="27" t="s">
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="27" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="27" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="27" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="27"/>
-    </row>
-    <row r="38" spans="3:3">
-      <c r="C38" s="23" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" s="28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="27" t="s">
+      <c r="D38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="6" t="s">
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="28"/>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="6" t="s">
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="23" t="s">
+      <c r="B41" s="6" t="s">
         <v>53</v>
       </c>
+      <c r="D41" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="42" spans="3:3">
-      <c r="C42" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" s="6" t="s">
+      <c r="C42" s="22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="6" t="s">
+    <row r="44" spans="3:3">
+      <c r="C44" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="4:6">
+    <row r="45" spans="4:4">
       <c r="D45" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="46" spans="4:4">
       <c r="D46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="6:6">
+      <c r="F48" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="4:4">
-      <c r="D48" s="6" t="s">
+    <row r="49" spans="4:4">
+      <c r="D49" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="5:5">
-      <c r="E49" s="6" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="3:3">
-      <c r="C51" s="23" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="6" t="s">
+    <row r="52" spans="5:5">
+      <c r="E52" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="6" t="s">
+    <row r="54" spans="3:3">
+      <c r="C54" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D53" s="6" t="s">
+    </row>
+    <row r="55" spans="4:4">
+      <c r="D55" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="3:5">
-      <c r="C55" s="31"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-    </row>
-    <row r="56" spans="3:5">
-      <c r="C56" s="31"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-    </row>
-    <row r="57" spans="3:5">
-      <c r="C57" s="31"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-    </row>
-    <row r="58" spans="3:5">
-      <c r="C58" s="31"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-    </row>
-    <row r="59" spans="3:5">
-      <c r="C59" s="31"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-    </row>
-    <row r="60" spans="3:5">
-      <c r="C60" s="31"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-    </row>
-    <row r="61" spans="3:5">
-      <c r="C61" s="31"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-    </row>
-    <row r="62" spans="3:5">
-      <c r="C62" s="31"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-    </row>
-    <row r="63" spans="3:5">
-      <c r="C63" s="31"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-    </row>
-    <row r="64" spans="3:5">
-      <c r="C64" s="31"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-    </row>
-    <row r="65" spans="3:5">
-      <c r="C65" s="31"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
+    <row r="56" spans="1:4">
+      <c r="A56" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="142" orientation="portrait"/>
   <headerFooter/>
@@ -3741,32 +3987,32 @@
     </row>
     <row r="12" ht="31" spans="5:5">
       <c r="E12" s="3" t="s">
-        <v>598</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" ht="31" spans="5:5">
       <c r="E13" s="3" t="s">
-        <v>599</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" ht="46.5" spans="5:5">
       <c r="E15" s="3" t="s">
-        <v>600</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" ht="62" spans="5:5">
       <c r="E16" s="4" t="s">
-        <v>601</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" ht="46.5" spans="5:5">
       <c r="E18" s="4" t="s">
-        <v>602</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19" spans="5:5">
       <c r="E19" s="5" t="s">
-        <v>603</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -3778,803 +4024,837 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.54615384615385" style="23" customWidth="1"/>
-    <col min="4" max="5" width="2.54615384615385" style="6" customWidth="1"/>
-    <col min="6" max="6" width="27.7538461538462" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="1" width="25.5" style="34" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="34" customWidth="1"/>
+    <col min="3" max="3" width="2.54615384615385" style="35" customWidth="1"/>
+    <col min="4" max="5" width="2.54615384615385" style="34" customWidth="1"/>
+    <col min="6" max="6" width="54.2384615384615" style="34" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="6" t="s">
-        <v>67</v>
+      <c r="B1" s="34" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="34" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="23" t="s">
-        <v>68</v>
+      <c r="C3" s="35" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="4:4">
-      <c r="D4" s="6" t="s">
-        <v>69</v>
+      <c r="D4" s="34" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="29" t="s">
-        <v>70</v>
+      <c r="C6" s="36" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="29" t="s">
-        <v>71</v>
+      <c r="C7" s="36" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="33" t="s">
-        <v>72</v>
+      <c r="C9" s="37" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="C11" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="29"/>
-      <c r="D12" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="14"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="14"/>
+      <c r="A13" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" spans="3:6">
-      <c r="C14" s="29"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>78</v>
+      <c r="C14" s="36"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14" t="s">
-        <v>80</v>
+      <c r="A15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="3:5">
-      <c r="C16" s="29"/>
-      <c r="D16" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="14"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="29"/>
-      <c r="D17" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="14"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="29"/>
-      <c r="D18" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="14"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="29"/>
-      <c r="D19" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="14"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="3:5">
-      <c r="C20" s="29"/>
-      <c r="D20" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="14"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="29"/>
-      <c r="D21" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="14"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="29"/>
-      <c r="D22" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="14"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="3:5">
-      <c r="C23" s="29"/>
-      <c r="D23" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="14"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="29"/>
-      <c r="D24" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="14"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="38"/>
     </row>
     <row r="25" spans="3:5">
-      <c r="C25" s="29"/>
-      <c r="D25" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="14"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="38"/>
     </row>
     <row r="26" spans="3:5">
-      <c r="C26" s="29"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27" spans="3:3">
-      <c r="C27" s="29" t="s">
-        <v>91</v>
+      <c r="C27" s="36" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="3:3">
-      <c r="C28" s="29" t="s">
-        <v>92</v>
+      <c r="C28" s="36" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="29"/>
+      <c r="A29" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="36"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:5">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:6">
-      <c r="A31" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
+      <c r="A31" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:6">
-      <c r="A32" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
+      <c r="A32" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:6">
-      <c r="A33" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
+      <c r="A33" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="42"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:6">
-      <c r="A34" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
+      <c r="A34" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:6">
-      <c r="A35" s="35"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:6">
-      <c r="A36" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="35"/>
+      <c r="A36" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="40"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:6">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="35"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="36"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="40"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:6">
-      <c r="A38" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="35"/>
+      <c r="A38" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="40"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:6">
-      <c r="A39" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="35"/>
+      <c r="A39" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="38"/>
+      <c r="F39" s="40"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:6">
-      <c r="A40" s="14"/>
-      <c r="B40" s="15" t="s">
+      <c r="A40" s="38"/>
+      <c r="B40" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="36"/>
+      <c r="D40" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="38"/>
+      <c r="F40" s="40"/>
+    </row>
+    <row r="41" ht="16" customHeight="1" spans="1:6">
+      <c r="A41" s="40"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1" spans="1:6">
+      <c r="A42" s="40"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+    </row>
+    <row r="43" ht="28" spans="1:6">
+      <c r="A43" s="40"/>
+      <c r="B43" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" ht="98" spans="1:6">
+      <c r="A44" s="40"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1" spans="1:6">
+      <c r="A45" s="40"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1" spans="1:6">
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+    </row>
+    <row r="47" ht="16" customHeight="1" spans="1:6">
+      <c r="A47" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="35"/>
-    </row>
-    <row r="41" ht="16" customHeight="1" spans="1:6">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:6">
-      <c r="A42" s="35"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-    </row>
-    <row r="43" ht="16" customHeight="1" spans="1:6">
-      <c r="A43" s="35"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-    </row>
-    <row r="44" ht="16" customHeight="1" spans="1:6">
-      <c r="A44" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-    </row>
-    <row r="45" ht="16" customHeight="1" spans="1:6">
-      <c r="A45" s="35"/>
-      <c r="B45" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-    </row>
-    <row r="46" ht="16" customHeight="1" spans="1:6">
-      <c r="A46" s="35"/>
-      <c r="B46" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-    </row>
-    <row r="47" ht="16" customHeight="1" spans="1:6">
-      <c r="A47" s="35"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
+      <c r="B47" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:6">
-      <c r="A48" s="35"/>
-      <c r="B48" s="35"/>
-      <c r="C48" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="42"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:6">
-      <c r="A49" s="35"/>
-      <c r="B49" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" s="37"/>
-      <c r="D49" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="42"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:6">
-      <c r="A50" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="35"/>
-      <c r="C50" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:6">
-      <c r="A51" s="35"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:6">
-      <c r="A52" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
+      <c r="A52" s="40"/>
+      <c r="B52" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="42"/>
+      <c r="D52" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:6">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
+      <c r="A53" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:6">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
+      <c r="A54" s="40"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:6">
-      <c r="A55" s="35"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35" t="s">
-        <v>127</v>
-      </c>
+      <c r="A55" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:6">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
+      <c r="A56" s="40"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:6">
-      <c r="A57" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35" t="s">
-        <v>130</v>
-      </c>
+      <c r="A57" s="40"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:6">
-      <c r="A58" s="35"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
+      <c r="A58" s="40"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:6">
-      <c r="A59" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35" t="s">
-        <v>133</v>
-      </c>
+      <c r="A59" s="40"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:6">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
+      <c r="A60" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="40"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:6">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
+      <c r="A61" s="40"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:6">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
+      <c r="A62" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="40"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:6">
-      <c r="A63" s="35"/>
-      <c r="B63" s="35"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
+      <c r="A63" s="40"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:6">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
+      <c r="A64" s="40"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:6">
-      <c r="A65" s="35"/>
-      <c r="B65" s="35"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35" t="s">
-        <v>139</v>
-      </c>
+      <c r="A65" s="40"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:6">
-      <c r="A66" s="35"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
+      <c r="A66" s="40"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:6">
-      <c r="A67" s="35"/>
-      <c r="B67" s="35"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:6">
-      <c r="A68" s="35"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-    </row>
-    <row r="69" ht="42" spans="1:6">
-      <c r="A69" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="B69" s="35"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="36" t="s">
-        <v>144</v>
-      </c>
+      <c r="A68" s="40"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1" spans="1:6">
+      <c r="A69" s="40"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="1:6">
-      <c r="A70" s="35"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
+      <c r="A70" s="40"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="1:6">
-      <c r="A71" s="35"/>
-      <c r="B71" s="35"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-    </row>
-    <row r="72" ht="16" customHeight="1" spans="1:6">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
+      <c r="A71" s="40"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+    </row>
+    <row r="72" ht="42" spans="1:6">
+      <c r="A72" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="40"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="41" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1" spans="1:6">
-      <c r="A73" s="35"/>
-      <c r="B73" s="35"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
+      <c r="A73" s="40"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="1:6">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="1:6">
-      <c r="A75" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="35"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="1:6">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="1:6">
-      <c r="A77" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="B77" s="35"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="1:6">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
+      <c r="A78" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" s="40"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="1:6">
-      <c r="A79" s="35"/>
-      <c r="B79" s="35"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35" t="s">
-        <v>156</v>
-      </c>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="1:6">
-      <c r="A80" s="35"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
+      <c r="A80" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="40"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="1:6">
-      <c r="A81" s="35"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-    </row>
-    <row r="82" ht="28" spans="1:6">
-      <c r="A82" s="35"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="36" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="8"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-    </row>
-    <row r="86" spans="3:4">
-      <c r="C86" s="29"/>
-      <c r="D86" s="14"/>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="39" t="s">
+      <c r="A81" s="40"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="14"/>
-      <c r="C87" s="29" t="s">
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+    </row>
+    <row r="82" ht="16" customHeight="1" spans="1:6">
+      <c r="A82" s="40"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="40" t="s">
+    <row r="83" ht="16" customHeight="1" spans="1:6">
+      <c r="A83" s="40"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="40" t="s">
         <v>165</v>
+      </c>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+    </row>
+    <row r="84" ht="16" customHeight="1" spans="1:6">
+      <c r="A84" s="40"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+    </row>
+    <row r="85" ht="28" spans="1:6">
+      <c r="A85" s="40"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="41" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="45"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D86" s="38"/>
+      <c r="E86" s="45"/>
+      <c r="F86" s="45"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="45"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D87" s="38"/>
+      <c r="E87" s="45"/>
+      <c r="F87" s="45"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="45"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E88" s="45"/>
+      <c r="F88" s="45"/>
+    </row>
+    <row r="89" spans="3:4">
+      <c r="C89" s="36"/>
+      <c r="D89" s="38"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="38"/>
+      <c r="C90" s="36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A87" r:id="rId1" display="docs.python.org/3/library/stdtypes.html#binary-sequence-types-bytes-bytearray-memoryview"/>
+    <hyperlink ref="A90" r:id="rId1" display="docs.python.org/3/library/stdtypes.html#binary-sequence-types-bytes-bytearray-memoryview"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4584,771 +4864,803 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.9153846153846" style="6" customWidth="1"/>
     <col min="2" max="2" width="16.3461538461538" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.66923076923077" style="23" customWidth="1"/>
-    <col min="4" max="4" width="3.83076923076923" style="6" customWidth="1"/>
-    <col min="5" max="5" width="3.23076923076923" style="24" customWidth="1"/>
+    <col min="3" max="3" width="2.24615384615385" style="22" customWidth="1"/>
+    <col min="4" max="4" width="2.24615384615385" style="6" customWidth="1"/>
+    <col min="5" max="5" width="2.24615384615385" style="25" customWidth="1"/>
     <col min="6" max="6" width="40.9538461538462" style="6" customWidth="1"/>
     <col min="7" max="16384" width="8.66923076923077" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>168</v>
+        <v>175</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="3:3">
-      <c r="C4" s="23" t="s">
-        <v>169</v>
+      <c r="C4" s="22" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="6:6">
-      <c r="F7" s="25" t="s">
-        <v>174</v>
+      <c r="F7" s="26" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>176</v>
+      <c r="A8" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4">
-      <c r="D11" s="6" t="s">
-        <v>172</v>
+        <v>185</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6">
+      <c r="F11" s="25" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="5:5">
-      <c r="E13" s="24" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="5:5">
-      <c r="E15" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    <row r="13" spans="4:4">
+      <c r="D13" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6">
+      <c r="F14" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="6:6">
+      <c r="F15" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6">
+      <c r="F17" s="25" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="6" t="s">
+        <v>196</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>190</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="5:5">
-      <c r="E22" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="4:4">
-      <c r="D24" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" ht="14.5" spans="2:6">
-      <c r="B25" s="26" t="s">
-        <v>194</v>
-      </c>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" s="25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
       <c r="D25" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" s="19"/>
-    </row>
-    <row r="27" ht="14.5" spans="2:4">
-      <c r="B27" s="26"/>
-      <c r="D27" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" ht="14.5" spans="2:2">
-      <c r="B28" s="26"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5" spans="2:6">
+      <c r="B26" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" ht="14.5" spans="2:4">
+      <c r="B28" s="27"/>
+      <c r="D28" s="6" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" ht="14.5" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" spans="2:2">
-      <c r="B30" s="26"/>
-    </row>
-    <row r="31" ht="14.5" spans="2:3">
-      <c r="B31" s="26"/>
-      <c r="C31" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" ht="14.5" spans="2:6">
-      <c r="B32" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="33" ht="14.5" spans="2:3">
-      <c r="B33" s="26"/>
-      <c r="C33" s="23" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" ht="14.5" spans="2:2">
-      <c r="B34" s="26"/>
-    </row>
-    <row r="35" spans="1:2">
+        <v>208</v>
+      </c>
+      <c r="B29" s="27"/>
+      <c r="C29" s="22" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5" spans="2:3">
+      <c r="B30" s="27"/>
+      <c r="C30" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" ht="14.5" spans="2:6">
+      <c r="B31" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" ht="14.5" spans="2:3">
+      <c r="B32" s="27"/>
+      <c r="C32" s="22" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6">
+      <c r="C34" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5">
-      <c r="C36" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>218</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="25"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="D36" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="25"/>
+    </row>
+    <row r="37" ht="42" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>191</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="D38" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="23" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="51" spans="3:3">
-      <c r="C51" s="23" t="s">
+      <c r="F38" s="25" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="6" t="s">
+    <row r="39" spans="6:6">
+      <c r="F39" s="25"/>
+    </row>
+    <row r="40" spans="4:6">
+      <c r="D40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" s="25"/>
+    </row>
+    <row r="41" spans="4:6">
+      <c r="D41" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
+      <c r="F42" s="25" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="22" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="6" t="s">
+        <v>238</v>
+      </c>
       <c r="B53" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6">
+        <v>239</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
       <c r="B54" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>241</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
+        <v>244</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
       <c r="B56" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>236</v>
+        <v>247</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="6" t="s">
-        <v>238</v>
-      </c>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4">
       <c r="D59" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="61" spans="4:4">
-      <c r="D61" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="62" spans="5:5">
-      <c r="E62" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>172</v>
-      </c>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="6:6">
+      <c r="F60" s="25" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="6:6">
+      <c r="F63" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="6:6">
       <c r="F64" s="6" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="6:6">
-      <c r="F65" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="66" spans="6:6">
-      <c r="F66" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="67" spans="6:6">
-      <c r="F67" s="25" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="68" spans="4:4">
-      <c r="D68" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" s="23" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="72" spans="4:4">
-      <c r="D72" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E73" s="24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F65" s="26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4">
+      <c r="D66" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3">
+      <c r="C69" s="22" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4">
+      <c r="D70" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6">
+      <c r="F73" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E74" s="24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="75" spans="5:5">
-      <c r="E75" s="24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="6" t="s">
-        <v>259</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76" spans="4:6">
       <c r="D76" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="4:4">
-      <c r="D77" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" spans="4:6">
+        <v>180</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4">
       <c r="D78" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="80" spans="4:4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="6" t="s">
+        <v>273</v>
+      </c>
       <c r="D80" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>185</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="6" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="83" spans="6:6">
+      <c r="F83" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="84" ht="14.5" spans="6:6">
+      <c r="F84" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
       <c r="B85" s="6" t="s">
-        <v>269</v>
+        <v>280</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="89" spans="4:4">
+        <v>282</v>
+      </c>
+      <c r="D86" s="22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="6" t="s">
+        <v>285</v>
+      </c>
       <c r="D89" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="90" spans="4:6">
-      <c r="D90" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>274</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="4:4">
       <c r="D91" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="6" t="s">
-        <v>259</v>
-      </c>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="92" spans="4:6">
       <c r="D92" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="94" spans="3:3">
-      <c r="C94" s="23" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="102" spans="3:3">
-      <c r="C102" s="29" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="103" spans="3:4">
-      <c r="C103" s="29"/>
-      <c r="D103" s="14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="104" spans="3:5">
-      <c r="C104" s="29"/>
-      <c r="E104" s="24" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="105" spans="3:4">
-      <c r="C105" s="29"/>
-      <c r="D105" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="106" spans="3:5">
-      <c r="C106" s="29"/>
-      <c r="E106" s="24" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="107" spans="3:4">
-      <c r="C107" s="29"/>
-      <c r="D107" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="108" spans="3:3">
-      <c r="C108" s="29"/>
+        <v>180</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3">
+      <c r="C95" s="22" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3">
+      <c r="C97" s="24" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4">
+      <c r="C98" s="24"/>
+      <c r="D98" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="99" spans="3:6">
+      <c r="C99" s="24"/>
+      <c r="F99" s="25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="100" spans="3:6">
+      <c r="C100" s="24"/>
+      <c r="D100" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F100" s="25"/>
+    </row>
+    <row r="101" spans="3:6">
+      <c r="C101" s="24"/>
+      <c r="F101" s="25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4">
+      <c r="C102" s="24"/>
+      <c r="D102" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3">
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="31"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="31"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="31"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="31"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="31"/>
+      <c r="E105" s="33"/>
+      <c r="F105" s="31"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="31"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="31"/>
+      <c r="E106" s="33"/>
+      <c r="F106" s="31"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="31"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="31"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="31"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="31"/>
+      <c r="B108" s="31"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="31"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="31"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="30"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="31"/>
-      <c r="D109" s="30"/>
-      <c r="E109" s="32"/>
-      <c r="F109" s="30"/>
+      <c r="A109" s="31"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="32"/>
+      <c r="D109" s="31"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="31"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="30"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="31"/>
-      <c r="D110" s="30"/>
-      <c r="E110" s="32"/>
-      <c r="F110" s="30"/>
+      <c r="A110" s="31"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="32"/>
+      <c r="D110" s="31"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="31"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="30"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="31"/>
-      <c r="D111" s="30"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="30"/>
+      <c r="A111" s="31"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="31"/>
+      <c r="E111" s="33"/>
+      <c r="F111" s="31"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="30"/>
-      <c r="B112" s="30"/>
-      <c r="C112" s="31"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="32"/>
-      <c r="F112" s="30"/>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="30"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="31"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="30"/>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" s="30"/>
-      <c r="B114" s="30"/>
-      <c r="C114" s="31"/>
-      <c r="D114" s="30"/>
-      <c r="E114" s="32"/>
-      <c r="F114" s="30"/>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="31"/>
-      <c r="D115" s="30"/>
-      <c r="E115" s="32"/>
-      <c r="F115" s="30"/>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="31"/>
-      <c r="D116" s="30"/>
-      <c r="E116" s="32"/>
-      <c r="F116" s="30"/>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="31"/>
-      <c r="D117" s="30"/>
-      <c r="E117" s="32"/>
-      <c r="F117" s="30"/>
-    </row>
-    <row r="128" spans="3:4">
-      <c r="C128" s="29"/>
+      <c r="A112" s="31"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="32"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="31"/>
+    </row>
+    <row r="123" spans="3:4">
+      <c r="C123" s="24"/>
+      <c r="D123" s="14"/>
+    </row>
+    <row r="124" spans="3:4">
+      <c r="C124" s="24"/>
+      <c r="D124" s="14"/>
+    </row>
+    <row r="125" spans="3:4">
+      <c r="C125" s="24"/>
+      <c r="D125" s="14"/>
+    </row>
+    <row r="126" spans="3:4">
+      <c r="C126" s="24"/>
+      <c r="D126" s="14"/>
+    </row>
+    <row r="127" spans="3:4">
+      <c r="C127" s="24"/>
+      <c r="D127" s="14"/>
+    </row>
+    <row r="128" spans="4:4">
       <c r="D128" s="14"/>
     </row>
     <row r="129" spans="3:4">
-      <c r="C129" s="29"/>
+      <c r="C129" s="24"/>
       <c r="D129" s="14"/>
-    </row>
-    <row r="130" spans="3:4">
-      <c r="C130" s="29"/>
-      <c r="D130" s="14"/>
-    </row>
-    <row r="131" spans="3:4">
-      <c r="C131" s="29"/>
-      <c r="D131" s="14"/>
-    </row>
-    <row r="132" spans="3:4">
-      <c r="C132" s="29"/>
-      <c r="D132" s="14"/>
-    </row>
-    <row r="133" spans="4:4">
-      <c r="D133" s="14"/>
-    </row>
-    <row r="134" spans="3:4">
-      <c r="C134" s="29"/>
-      <c r="D134" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5360,12 +5672,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="25.2538461538462" style="6" customWidth="1"/>
     <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="6" customWidth="1"/>
+    <col min="3" max="3" width="5.66923076923077" style="22" customWidth="1"/>
     <col min="4" max="4" width="7.08461538461538" style="6" customWidth="1"/>
     <col min="5" max="5" width="7.75384615384615" style="6" customWidth="1"/>
     <col min="6" max="6" width="12.1692307692308" style="6" customWidth="1"/>
@@ -5378,65 +5690,73 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="6" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>288</v>
+        <v>302</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="6" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="6" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>295</v>
+        <v>309</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>297</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5449,360 +5769,422 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14"/>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="25.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="6" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="6" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="22" customWidth="1"/>
-    <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="6"/>
+    <col min="3" max="3" width="2.46923076923077" style="22" customWidth="1"/>
+    <col min="4" max="5" width="2.46923076923077" style="6" customWidth="1"/>
+    <col min="6" max="6" width="64.4769230769231" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+    <row r="1" s="22" customFormat="1" ht="13" customHeight="1" spans="2:2">
+      <c r="B1" s="22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" s="22" customFormat="1" spans="1:5">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>301</v>
+        <v>317</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="6" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="6" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>321</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="4:4">
+        <v>323</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="D9" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
-        <v>311</v>
-      </c>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
       <c r="D10" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="D11" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5">
-      <c r="E12" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>319</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5">
+      <c r="E13" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="22" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="4:4">
-      <c r="D16" s="6" t="s">
-        <v>320</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="6:6">
+      <c r="F16" s="23" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="17" ht="98" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6">
+      <c r="F18" s="6" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="A19" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="14" t="s">
-        <v>323</v>
-      </c>
+      <c r="A21" s="14"/>
       <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14" t="s">
-        <v>324</v>
-      </c>
+      <c r="C21" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14" t="s">
-        <v>325</v>
-      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="E22" s="14"/>
       <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="14" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14" t="s">
-        <v>327</v>
-      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="E23" s="14"/>
       <c r="F23" s="14"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="C24" s="14"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="F24" s="14"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="14"/>
+      <c r="A25" s="14" t="s">
+        <v>346</v>
+      </c>
       <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="E25" s="14"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14" t="s">
+        <v>347</v>
+      </c>
       <c r="F25" s="14"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="14"/>
+        <v>348</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="F26" s="14"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="14" t="s">
+        <v>351</v>
+      </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+        <v>352</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="14" t="s">
+        <v>353</v>
+      </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" ht="15.5" spans="1:5">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-    </row>
-    <row r="30" ht="15.5" spans="1:9">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" ht="15.5" spans="1:9">
+    <row r="29" spans="1:6">
+      <c r="A29" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" ht="15.5" spans="1:5">
       <c r="A31"/>
       <c r="B31"/>
-      <c r="C31"/>
+      <c r="C31" s="1"/>
       <c r="D31"/>
       <c r="E31"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" ht="15.5" spans="1:9">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-    </row>
-    <row r="33" ht="15.5" spans="1:9">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-    </row>
-    <row r="34" spans="1:9">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-    </row>
-    <row r="36" spans="1:7">
+        <v>360</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="G36" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>344</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="6" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="39" spans="5:5">
-      <c r="E39" s="6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="6" t="s">
-        <v>352</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4">
+      <c r="D44" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="49" ht="28" spans="6:6">
+      <c r="F49" s="23" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4">
+      <c r="D50" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4">
+      <c r="D55" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4">
+      <c r="D57" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4">
+      <c r="D59" s="6" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5814,598 +6196,657 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:F110"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="25.4153846153846" style="17" customWidth="1"/>
     <col min="2" max="2" width="19.8307692307692" style="17" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="17" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="17" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="17" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="17" customWidth="1"/>
-    <col min="7" max="7" width="4.5" style="20" customWidth="1"/>
-    <col min="8" max="8" width="4.5" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="17"/>
+    <col min="3" max="3" width="2.07692307692308" style="20" customWidth="1"/>
+    <col min="4" max="4" width="3" style="17" customWidth="1"/>
+    <col min="5" max="5" width="2.38461538461538" style="17" customWidth="1"/>
+    <col min="6" max="6" width="48" style="17" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="2:8">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5">
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="3:5">
-      <c r="C4" s="15"/>
-      <c r="D4" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" spans="3:5">
-      <c r="C5" s="15"/>
-      <c r="D5" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="3:5">
-      <c r="C6" s="15"/>
-      <c r="D6" s="17" t="s">
-        <v>358</v>
-      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" s="20" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" s="17" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="6:6">
+      <c r="F5" s="21" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1" spans="1:5">
+      <c r="A6" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="D6" s="15"/>
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="15"/>
-      <c r="D7" s="17" t="s">
-        <v>359</v>
+      <c r="C7" s="16"/>
+      <c r="D7" s="15" t="s">
+        <v>400</v>
       </c>
       <c r="E7" s="15"/>
     </row>
     <row r="8" spans="3:5">
-      <c r="C8" s="15"/>
-      <c r="D8" s="15" t="s">
-        <v>360</v>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>401</v>
       </c>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="4:4">
+    <row r="9" spans="3:5">
+      <c r="C9" s="16"/>
       <c r="D9" s="17" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" spans="4:4">
-      <c r="D10" s="15" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4">
+        <v>402</v>
+      </c>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="10" spans="3:5">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" spans="3:5">
+      <c r="C11" s="16"/>
       <c r="D11" s="15" t="s">
-        <v>363</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="4:4">
-      <c r="D12" s="6" t="s">
-        <v>314</v>
+      <c r="D12" s="17" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="6" t="s">
-        <v>364</v>
+      <c r="D13" s="15" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="4:4">
-      <c r="D14" s="6" t="s">
-        <v>365</v>
+      <c r="D14" s="15" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="4:4">
-      <c r="D15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="16" spans="4:4">
-      <c r="D16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="6"/>
+      <c r="D17" s="6" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>367</v>
+        <v>410</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>369</v>
+        <v>412</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>371</v>
+        <v>414</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="17" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="17" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="17" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="17" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="17" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="17" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>380</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="17" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="17" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="17" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="3:3">
-      <c r="C31" s="17" t="s">
-        <v>386</v>
+      <c r="C31" s="20" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="17" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="17" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="17" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="15" t="s">
-        <v>397</v>
+      <c r="C35" s="16" t="s">
+        <v>441</v>
       </c>
       <c r="D35" s="15"/>
     </row>
     <row r="36" spans="3:4">
-      <c r="C36" s="15"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="15" t="s">
-        <v>398</v>
+        <v>442</v>
       </c>
     </row>
     <row r="37" spans="3:4">
-      <c r="C37" s="15"/>
+      <c r="C37" s="16"/>
       <c r="D37" s="15" t="s">
-        <v>399</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="3:4">
-      <c r="C38" s="15" t="s">
-        <v>400</v>
+      <c r="C38" s="16" t="s">
+        <v>444</v>
       </c>
       <c r="D38" s="15"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="15"/>
+      <c r="C39" s="16"/>
       <c r="D39" s="15"/>
     </row>
     <row r="40" spans="3:4">
-      <c r="C40" s="15" t="s">
-        <v>401</v>
+      <c r="C40" s="16" t="s">
+        <v>445</v>
       </c>
       <c r="D40" s="15"/>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="15"/>
+      <c r="C41" s="16"/>
       <c r="D41" s="15" t="s">
-        <v>402</v>
+        <v>446</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>404</v>
+        <v>447</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="17" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="45" spans="5:5">
-      <c r="E45" s="17" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="47" spans="4:4">
-      <c r="D47" s="17" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="48" spans="5:5">
-      <c r="E48" s="17" t="s">
-        <v>409</v>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" ht="28" spans="6:6">
+      <c r="F45" s="21" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="46" spans="6:6">
+      <c r="F46" s="21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="6:6">
+      <c r="F47" s="17" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="17" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5">
-      <c r="E50" s="17" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="17" t="s">
-        <v>412</v>
-      </c>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
       <c r="D51" s="17" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3">
-      <c r="C52" s="17" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="53" spans="4:5">
-      <c r="D53" s="17" t="s">
-        <v>415</v>
-      </c>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="17" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5">
       <c r="E53" s="17" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="17" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="55" spans="4:4">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="17" t="s">
+        <v>459</v>
+      </c>
       <c r="D55" s="17" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3">
-      <c r="C59" s="17" t="s">
-        <v>426</v>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" s="20" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="58" spans="4:5">
+      <c r="D58" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="59" spans="5:5">
+      <c r="E59" s="17" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="17" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="61" spans="3:3">
-      <c r="C61" s="17" t="s">
-        <v>428</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="17" t="s">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="17" t="s">
+        <v>471</v>
+      </c>
       <c r="B63" s="17" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" spans="3:3">
-      <c r="C64" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="65" spans="4:5">
+      <c r="C64" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="65" spans="4:4">
       <c r="D65" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="17" t="s">
-        <v>437</v>
-      </c>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" s="20" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
       <c r="B67" s="17" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="17" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="17" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" s="17" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="72" spans="4:4">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3">
+      <c r="C69" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="70" spans="4:6">
+      <c r="D70" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="5:5">
+      <c r="E71" s="17" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="17" t="s">
+        <v>483</v>
+      </c>
       <c r="D72" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4">
-      <c r="D73" s="17" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="74" spans="4:4">
-      <c r="D74" s="17" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="75" spans="4:4">
-      <c r="D75" s="17" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>484</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6">
+      <c r="F73" s="17" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="74" spans="6:6">
+      <c r="F74" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="75" spans="6:6">
+      <c r="F75" s="17" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
+        <v>489</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
       <c r="B77" s="17" t="s">
-        <v>449</v>
-      </c>
-      <c r="D77" s="17" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="79" spans="4:4">
-      <c r="D79" s="17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3">
-      <c r="B80" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="C80" s="17" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3">
-      <c r="C81" s="17" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="83" spans="4:4">
-      <c r="D83" s="17" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="84" spans="4:4">
-      <c r="D84" s="17" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="86" spans="3:3">
-      <c r="C86" s="17" t="s">
-        <v>463</v>
+        <v>491</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="78" spans="5:5">
+      <c r="E78" s="17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="79" spans="5:5">
+      <c r="E79" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="17" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3">
+      <c r="C85" s="20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="17" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="17" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="17" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="C91" s="17" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="92" spans="4:4">
-      <c r="D92" s="17" t="s">
-        <v>468</v>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="17" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="17" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="17" t="s">
-        <v>470</v>
-      </c>
-      <c r="C94" s="17" t="s">
-        <v>471</v>
-      </c>
-      <c r="G94" s="20">
-        <v>5</v>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3">
+      <c r="C95" s="20" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4">
+      <c r="D97" s="17" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4">
+      <c r="D98" s="17" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3">
+      <c r="C100" s="20" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4">
+      <c r="D101" s="17" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4">
+      <c r="D102" s="17" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4">
+      <c r="D105" s="17" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="106" spans="4:4">
+      <c r="D106" s="17" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3">
+      <c r="C110" s="20" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -6433,7 +6874,7 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" s="6" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -6445,52 +6886,52 @@
         <v>4</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="6" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>473</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="6" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>475</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="6" t="s">
-        <v>476</v>
+        <v>534</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>477</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="6" t="s">
-        <v>478</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="6" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>480</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="6:6">
       <c r="F8" s="6" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -6514,37 +6955,37 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="13" t="s">
-        <v>482</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="13" t="s">
-        <v>483</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="13" t="s">
-        <v>484</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" ht="14" spans="4:4">
       <c r="D8" s="14" t="s">
-        <v>485</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="13" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="13" t="s">
-        <v>487</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" ht="14" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -6552,7 +6993,7 @@
     </row>
     <row r="14" ht="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -6561,50 +7002,50 @@
     <row r="15" ht="14" spans="1:4">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>490</v>
+        <v>548</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="D15" s="15"/>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="15"/>
       <c r="B16" s="15" t="s">
-        <v>492</v>
+        <v>550</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="D16" s="15"/>
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>494</v>
+        <v>552</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="D17" s="15"/>
     </row>
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="15"/>
       <c r="B18" s="16" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="D18" s="15"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="15"/>
       <c r="B19" s="16" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="D19" s="15"/>
     </row>
@@ -6612,244 +7053,244 @@
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="D20" s="15"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="15"/>
       <c r="B21" s="15" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>502</v>
+        <v>560</v>
       </c>
       <c r="D21" s="15"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="15"/>
       <c r="B22" s="15" t="s">
-        <v>503</v>
+        <v>561</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="D22" s="15"/>
     </row>
     <row r="23" ht="14" spans="1:4">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="s">
-        <v>505</v>
+        <v>563</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>506</v>
+        <v>564</v>
       </c>
       <c r="D23" s="15"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="15"/>
       <c r="B24" s="15" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="D24" s="15"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="15"/>
       <c r="B25" s="15" t="s">
-        <v>509</v>
+        <v>567</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="D25" s="15"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>510</v>
+        <v>568</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="D26" s="15"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="15"/>
       <c r="B27" s="15" t="s">
-        <v>483</v>
+        <v>541</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="D27" s="15"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="15"/>
       <c r="B28" s="15" t="s">
-        <v>512</v>
+        <v>570</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="D28" s="15"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="15"/>
       <c r="B29" s="15" t="s">
-        <v>513</v>
+        <v>571</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="D29" s="15"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="15"/>
       <c r="B30" s="15" t="s">
-        <v>514</v>
+        <v>572</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>515</v>
+        <v>573</v>
       </c>
       <c r="D30" s="15"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="15"/>
       <c r="B31" s="15" t="s">
-        <v>516</v>
+        <v>574</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
       <c r="D31" s="15"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="15"/>
       <c r="B32" s="15" t="s">
-        <v>518</v>
+        <v>576</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="D32" s="15"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="15"/>
       <c r="B33" s="15" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="D33" s="15"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="15"/>
       <c r="B34" s="15" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>523</v>
+        <v>581</v>
       </c>
       <c r="D34" s="15"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="15"/>
       <c r="B35" s="15" t="s">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="D35" s="15"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="15"/>
       <c r="B36" s="15" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>526</v>
+        <v>584</v>
       </c>
       <c r="D36" s="15"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="15"/>
       <c r="B37" s="15" t="s">
-        <v>527</v>
+        <v>585</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>528</v>
+        <v>586</v>
       </c>
       <c r="D37" s="15"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="15"/>
       <c r="B38" s="15" t="s">
-        <v>529</v>
+        <v>587</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>530</v>
+        <v>588</v>
       </c>
       <c r="D38" s="15"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="15"/>
       <c r="B39" s="15" t="s">
-        <v>531</v>
+        <v>589</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="D39" s="15"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="15"/>
       <c r="B40" s="15" t="s">
-        <v>533</v>
+        <v>591</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>534</v>
+        <v>592</v>
       </c>
       <c r="D40" s="15"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="15"/>
       <c r="B41" s="15" t="s">
-        <v>535</v>
+        <v>593</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="D41" s="15"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="15"/>
       <c r="B42" s="15" t="s">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="D42" s="15"/>
     </row>
     <row r="44" ht="14" spans="2:3">
       <c r="B44" s="17" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
     </row>
     <row r="46" ht="14" spans="2:3">
       <c r="B46" s="18" t="s">
-        <v>541</v>
+        <v>599</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>542</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -6869,12 +7310,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="6" t="s">
-        <v>543</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>544</v>
+        <v>602</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6882,7 +7323,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -6890,32 +7331,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="10" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="11" t="s">
-        <v>548</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="11" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="11" t="s">
-        <v>550</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="10" t="s">
-        <v>551</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -6923,7 +7364,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="9" t="s">
-        <v>552</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -6931,32 +7372,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="10" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="11" t="s">
-        <v>554</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="11" t="s">
-        <v>555</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="11" t="s">
-        <v>556</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="10" t="s">
-        <v>557</v>
+        <v>615</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -6964,51 +7405,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="9" t="s">
-        <v>558</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>560</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="8"/>
       <c r="B24" s="6" t="s">
-        <v>561</v>
+        <v>619</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="10" t="s">
-        <v>562</v>
+        <v>620</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="11" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="11" t="s">
-        <v>564</v>
+        <v>622</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="11" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="10" t="s">
-        <v>566</v>
+        <v>624</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -7016,7 +7457,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="9" t="s">
-        <v>567</v>
+        <v>625</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -7024,32 +7465,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="10" t="s">
-        <v>568</v>
+        <v>626</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="11" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="11" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="11" t="s">
-        <v>571</v>
+        <v>629</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="10" t="s">
-        <v>572</v>
+        <v>630</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -7057,7 +7498,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="9" t="s">
-        <v>573</v>
+        <v>631</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -7065,32 +7506,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="10" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="11" t="s">
-        <v>575</v>
+        <v>633</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="11" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="11" t="s">
-        <v>577</v>
+        <v>635</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="10" t="s">
-        <v>578</v>
+        <v>636</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -7098,7 +7539,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="9" t="s">
-        <v>579</v>
+        <v>637</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -7106,32 +7547,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="10" t="s">
-        <v>580</v>
+        <v>638</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="11" t="s">
-        <v>581</v>
+        <v>639</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="11" t="s">
-        <v>582</v>
+        <v>640</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="11" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="10" t="s">
-        <v>584</v>
+        <v>642</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -7139,7 +7580,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="9" t="s">
-        <v>585</v>
+        <v>643</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -7147,32 +7588,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="10" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="10" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="11" t="s">
-        <v>587</v>
+        <v>645</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="11" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="11" t="s">
-        <v>589</v>
+        <v>647</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="10" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -7180,37 +7621,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="9" t="s">
-        <v>591</v>
+        <v>649</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="7" t="s">
-        <v>592</v>
+        <v>650</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="6" t="s">
-        <v>593</v>
+        <v>651</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="6" t="s">
-        <v>594</v>
+        <v>652</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="12" t="s">
-        <v>595</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="6" t="s">
-        <v>596</v>
+        <v>654</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="6" t="s">
-        <v>597</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="880" firstSheet="3" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="880" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="intermed" sheetId="5" r:id="rId4"/>
     <sheet name="adv" sheetId="15" r:id="rId5"/>
     <sheet name="module" sheetId="9" r:id="rId6"/>
-    <sheet name="py-ques" sheetId="6" r:id="rId7"/>
+    <sheet name="x-qs" sheetId="6" r:id="rId7"/>
     <sheet name="other topics" sheetId="12" r:id="rId8"/>
     <sheet name="ex libs" sheetId="20" r:id="rId9"/>
     <sheet name="info" sheetId="21" r:id="rId10"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="700">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -207,6 +207,42 @@
     <t>mixin pattern</t>
   </si>
   <si>
+    <t>first come definition is prioritised</t>
+  </si>
+  <si>
+    <t>Class mixins</t>
+  </si>
+  <si>
+    <t>Basics 404 Inheritance and Mixins</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">class VeggieSoup(FoodMixin, VeggieMixin, OverrideMixin, SoupMixin):
+pass </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t># means no further code for this definition</t>
+    </r>
+  </si>
+  <si>
+    <t># passing context to class
+OR
+# making an extended class</t>
+  </si>
+  <si>
     <t>objects</t>
   </si>
   <si>
@@ -401,6 +437,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>import re
 txt = "The rain in Spain"
 x = re.</t>
@@ -1027,12 +1069,6 @@
     <t>map lambda</t>
   </si>
   <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
     <t>self -&gt; basics -&gt; asyncio -&gt; wait-1</t>
   </si>
   <si>
@@ -1066,10 +1102,38 @@
     <t>inter-thread communication</t>
   </si>
   <si>
+    <t>https://github.com/gto76/python-cheatsheet?tab=readme-ov-file#threading</t>
+  </si>
+  <si>
     <t>tutorialspoint.com/python/python_userdefined_exception.htm</t>
   </si>
   <si>
     <t>User Define Exceptions</t>
+  </si>
+  <si>
+    <t>github.com/gto76/python-cheatsheet?tab=readme-ov-file#introspection</t>
+  </si>
+  <si>
+    <t>Introspection</t>
+  </si>
+  <si>
+    <t>&lt;list&gt; = dir()                      # Local names of variables, functions, classes and modules.
+&lt;dict&gt; = vars()                     # Dict of local names and their objects. Also locals().
+&lt;dict&gt; = globals()                  # Dict of global names and their objects, e.g. __builtin__.</t>
+  </si>
+  <si>
+    <t>&lt;list&gt; = dir(&lt;obj&gt;)                 # Returns names of object's attributes (including methods).
+&lt;dict&gt; = vars(&lt;obj&gt;)                # Returns dict of writable attributes. Also &lt;obj&gt;.__dict__.
+&lt;bool&gt; = hasattr(&lt;obj&gt;, '&lt;name&gt;')   # Checks if object possesses attribute with passed name.
+value  = getattr(&lt;obj&gt;, '&lt;name&gt;')   # Returns the object's attribute or raises AttributeError.
+setattr(&lt;obj&gt;, '&lt;name&gt;', value)     # Sets attribute. Only works on objects with __dict__ attr.
+delattr(&lt;obj&gt;, '&lt;name&gt;')            # Deletes attribute from __dict__. Also `del &lt;obj&gt;.&lt;name&gt;`.</t>
+  </si>
+  <si>
+    <t>v&lt;Sig&gt;  = inspect.signature(&lt;func&gt;)#Returns Signature obj of the passed func or class.
+&lt;dict&gt; = &lt;Sig&gt;.parameters           # Returns dict of Parameters. Also &lt;Sig&gt;.return_annotation.
+&lt;memb&gt; = &lt;Param&gt;.kind Returns ParameterKind member (Parameter.KEYWORD_ONLY, …).
+&lt;type&gt; = &lt;Param&gt;.annotation    # Returns Parameter.empty if missing. Also &lt;Param&gt;.default.</t>
   </si>
   <si>
     <t>Advance and less used things in py</t>
@@ -1727,6 +1791,12 @@
     <t>type validation</t>
   </si>
   <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
     <t>fibonacci</t>
   </si>
   <si>
@@ -1755,6 +1825,87 @@
   </si>
   <si>
     <t>from o and n, we can make on/no</t>
+  </si>
+  <si>
+    <t>anagrams group</t>
+  </si>
+  <si>
+    <t>substring</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>hidden anagram</t>
+  </si>
+  <si>
+    <t>kpalindrome</t>
+  </si>
+  <si>
+    <t>https://app.programiz.pro/community-challenges/python?ref=dvacb</t>
+  </si>
+  <si>
+    <t>Dashing Numbers</t>
+  </si>
+  <si>
+    <t>Pronic Numbers</t>
+  </si>
+  <si>
+    <t>Broken Keywords</t>
+  </si>
+  <si>
+    <t>Convert to Spongecase</t>
+  </si>
+  <si>
+    <t>Disarium Number</t>
+  </si>
+  <si>
+    <t>Ginorts Order</t>
+  </si>
+  <si>
+    <t>Coin Change Problem</t>
+  </si>
+  <si>
+    <t>Archilles Numbers</t>
+  </si>
+  <si>
+    <t>Numeric Seesaw</t>
+  </si>
+  <si>
+    <t>Subsequence with Largest Sum</t>
+  </si>
+  <si>
+    <t>Largest Gap b/w numbers or string characters</t>
+  </si>
+  <si>
+    <t>Largest Palindrome Subsequence</t>
+  </si>
+  <si>
+    <t>juggler seqence</t>
+  </si>
+  <si>
+    <t>consecutive common numbers</t>
+  </si>
+  <si>
+    <t>find fulcrum</t>
+  </si>
+  <si>
+    <t>Most repeated character in file</t>
+  </si>
+  <si>
+    <t>Primorial of a number</t>
+  </si>
+  <si>
+    <t>py process</t>
+  </si>
+  <si>
+    <t>py-mon</t>
+  </si>
+  <si>
+    <t>restart while debugging</t>
+  </si>
+  <si>
+    <t>watchdog</t>
   </si>
   <si>
     <t>pandas</t>
@@ -2402,6 +2553,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>For tasks that are heavily reliant on CPU computation (e.g., complex calculations, image processing), the GIL significantly limits the benefits of multithreading. Since only one thread can execute Python bytecode at a time,</t>
     </r>
     <r>
@@ -2418,6 +2576,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">To achieve true parallelism for CPU-bound tasks in Python, </t>
     </r>
     <r>
@@ -3197,9 +3362,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3231,21 +3395,35 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3285,13 +3463,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3633,333 +3805,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="27.3307692307692" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="22" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="6" customWidth="1"/>
-    <col min="5" max="5" width="3.07692307692308" style="6" customWidth="1"/>
-    <col min="6" max="6" width="57.4538461538462" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="11" style="6"/>
+    <col min="1" max="1" width="27.3307692307692" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="5" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="18" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="5" customWidth="1"/>
+    <col min="5" max="5" width="3.07692307692308" style="5" customWidth="1"/>
+    <col min="6" max="6" width="57.4538461538462" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22" t="s">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="22"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="4:4">
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="4:4">
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="3:3">
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" ht="28" spans="6:6">
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="3:3">
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" ht="28" spans="6:6">
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="3:3">
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="4:4">
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="4:4">
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="24" spans="4:5">
-      <c r="D24" s="14"/>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="25" spans="3:3">
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="4:4">
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32" spans="3:3">
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="34" spans="4:4">
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="28" t="s">
+      <c r="B35" s="31"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="31" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="28"/>
+      <c r="A39" s="31"/>
     </row>
     <row r="40" spans="3:3">
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="42" spans="3:3">
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="3:3">
-      <c r="C44" s="22" t="s">
+    <row r="43" spans="1:4">
+      <c r="A43" s="28" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="45" spans="4:4">
-      <c r="D45" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="4:4">
-      <c r="D46" s="6" t="s">
+    <row r="44" ht="28" spans="1:6">
+      <c r="A44" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="47" spans="4:4">
-      <c r="D47" s="6" t="s">
+      <c r="F44" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="6:6">
-      <c r="F48" s="6" t="s">
+    <row r="45" ht="42" spans="6:6">
+      <c r="F45" s="21" t="s">
         <v>60</v>
       </c>
     </row>
+    <row r="47" spans="3:3">
+      <c r="C47" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="49" spans="4:4">
-      <c r="D49" s="6" t="s">
-        <v>61</v>
+      <c r="D49" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="4:4">
-      <c r="D50" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="5:5">
-      <c r="E52" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="3:3">
-      <c r="C54" s="22" t="s">
+    <row r="51" spans="6:6">
+      <c r="F51" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="6" t="s">
+    <row r="52" spans="4:4">
+      <c r="D52" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="6" t="s">
+    <row r="53" spans="4:4">
+      <c r="D53" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="6" t="s">
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="5" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="5:5">
+      <c r="E55" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3981,38 +4174,38 @@
   </cols>
   <sheetData>
     <row r="11" spans="4:4">
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" ht="31" spans="5:5">
-      <c r="E12" s="3" t="s">
-        <v>656</v>
+      <c r="E12" s="2" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="13" ht="31" spans="5:5">
-      <c r="E13" s="3" t="s">
-        <v>657</v>
+      <c r="E13" s="2" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="15" ht="46.5" spans="5:5">
-      <c r="E15" s="3" t="s">
-        <v>658</v>
+      <c r="E15" s="2" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="16" ht="62" spans="5:5">
-      <c r="E16" s="4" t="s">
-        <v>659</v>
+      <c r="E16" s="3" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="18" ht="46.5" spans="5:5">
-      <c r="E18" s="4" t="s">
-        <v>660</v>
+      <c r="E18" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="19" spans="5:5">
-      <c r="E19" s="5" t="s">
-        <v>661</v>
+      <c r="E19" s="4" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -4027,829 +4220,817 @@
   <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="34" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="34" customWidth="1"/>
-    <col min="3" max="3" width="2.54615384615385" style="35" customWidth="1"/>
-    <col min="4" max="5" width="2.54615384615385" style="34" customWidth="1"/>
-    <col min="6" max="6" width="54.2384615384615" style="34" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="34"/>
+    <col min="1" max="1" width="25.5" style="37" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="37" customWidth="1"/>
+    <col min="3" max="3" width="2.54615384615385" style="38" customWidth="1"/>
+    <col min="4" max="5" width="2.54615384615385" style="37" customWidth="1"/>
+    <col min="6" max="6" width="54.2384615384615" style="37" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="34" t="s">
-        <v>69</v>
+      <c r="B1" s="37" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="37" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="35" t="s">
-        <v>71</v>
+      <c r="C3" s="38" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="4:4">
-      <c r="D4" s="34" t="s">
-        <v>72</v>
+      <c r="D4" s="37" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="36" t="s">
-        <v>73</v>
+      <c r="C6" s="39" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="36" t="s">
-        <v>74</v>
+      <c r="C7" s="39" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="37" t="s">
-        <v>75</v>
+      <c r="C9" s="40" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
+      <c r="C11" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="36"/>
-      <c r="D12" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="41"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="38"/>
+      <c r="A13" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="41"/>
     </row>
     <row r="14" spans="3:6">
-      <c r="C14" s="36"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>81</v>
+      <c r="C14" s="39"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38" t="s">
-        <v>83</v>
+      <c r="A15" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="3:5">
-      <c r="C16" s="36"/>
-      <c r="D16" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="41"/>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="36"/>
-      <c r="D17" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="41"/>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="36"/>
-      <c r="D18" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="41"/>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="36"/>
-      <c r="D19" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="41"/>
     </row>
     <row r="20" spans="3:5">
-      <c r="C20" s="36"/>
-      <c r="D20" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="41"/>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="36"/>
-      <c r="D21" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="41"/>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="36"/>
-      <c r="D22" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="41"/>
     </row>
     <row r="23" spans="3:5">
-      <c r="C23" s="36"/>
-      <c r="D23" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="41"/>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="36"/>
-      <c r="D24" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="41"/>
     </row>
     <row r="25" spans="3:5">
-      <c r="C25" s="36"/>
-      <c r="D25" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="41"/>
     </row>
     <row r="26" spans="3:5">
-      <c r="C26" s="36"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
     </row>
     <row r="27" spans="3:3">
-      <c r="C27" s="36" t="s">
-        <v>94</v>
+      <c r="C27" s="39" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="3:3">
-      <c r="C28" s="36" t="s">
-        <v>95</v>
+      <c r="C28" s="39" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="36"/>
+      <c r="A29" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="39"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:5">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:6">
-      <c r="A31" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
+      <c r="A31" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:6">
-      <c r="A32" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
+      <c r="A32" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="44"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:6">
-      <c r="A33" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
+      <c r="A33" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="45"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:6">
-      <c r="A34" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
+      <c r="A34" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:6">
-      <c r="A35" s="40"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:6">
-      <c r="A36" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="40"/>
+      <c r="A36" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="41"/>
+      <c r="C36" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="43"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:6">
-      <c r="A37" s="38"/>
-      <c r="B37" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="36"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="40"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="43"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:6">
-      <c r="A38" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="B38" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="40"/>
+      <c r="A38" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="43"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:6">
-      <c r="A39" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="36"/>
-      <c r="D39" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="38"/>
-      <c r="F39" s="40"/>
+      <c r="A39" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="41"/>
+      <c r="F39" s="43"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:6">
-      <c r="A40" s="38"/>
-      <c r="B40" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="40"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="41"/>
+      <c r="F40" s="43"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:6">
-      <c r="A41" s="40"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="40" t="s">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1" spans="1:6">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+    </row>
+    <row r="43" ht="28" spans="1:6">
+      <c r="A43" s="43"/>
+      <c r="B43" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" ht="98" spans="1:6">
+      <c r="A44" s="43"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1" spans="1:6">
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1" spans="1:6">
+      <c r="A46" s="43"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+    </row>
+    <row r="47" ht="16" customHeight="1" spans="1:6">
+      <c r="A47" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:6">
-      <c r="A42" s="40"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-    </row>
-    <row r="43" ht="28" spans="1:6">
-      <c r="A43" s="40"/>
-      <c r="B43" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" ht="98" spans="1:6">
-      <c r="A44" s="40"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="41" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1" spans="1:6">
-      <c r="A45" s="40"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1" spans="1:6">
-      <c r="A46" s="40"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-    </row>
-    <row r="47" ht="16" customHeight="1" spans="1:6">
-      <c r="A47" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" s="40"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
+      <c r="B47" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:6">
-      <c r="A48" s="40"/>
-      <c r="B48" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" s="45"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:6">
-      <c r="A49" s="40"/>
-      <c r="B49" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C49" s="42"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="A49" s="43"/>
+      <c r="B49" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="45"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:6">
-      <c r="A50" s="40"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
+      <c r="A50" s="43"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:6">
-      <c r="A51" s="40"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
+      <c r="A51" s="43"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:6">
-      <c r="A52" s="40"/>
-      <c r="B52" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" s="45"/>
+      <c r="D52" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:6">
-      <c r="A53" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
+      <c r="A53" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="43"/>
+      <c r="C53" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:6">
-      <c r="A54" s="40"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:6">
-      <c r="A55" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="40"/>
-      <c r="C55" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
+      <c r="A55" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="43"/>
+      <c r="C55" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:6">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
+      <c r="A56" s="43"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:6">
-      <c r="A57" s="40"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:6">
-      <c r="A58" s="40"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40" t="s">
-        <v>135</v>
+      <c r="A58" s="43"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:6">
-      <c r="A59" s="40"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" s="40"/>
-      <c r="F59" s="40"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:6">
-      <c r="A60" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="B60" s="40"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40" t="s">
-        <v>138</v>
+      <c r="A60" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" s="43"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:6">
-      <c r="A61" s="40"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" s="40"/>
-      <c r="F61" s="40"/>
+      <c r="A61" s="43"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" s="43"/>
+      <c r="F61" s="43"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:6">
-      <c r="A62" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="B62" s="40"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="40"/>
-      <c r="F62" s="40" t="s">
-        <v>141</v>
+      <c r="A62" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="43"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="43"/>
+      <c r="F62" s="43" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:6">
-      <c r="A63" s="40"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="43"/>
+      <c r="F63" s="43"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:6">
-      <c r="A64" s="40"/>
-      <c r="B64" s="40"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="E64" s="40"/>
-      <c r="F64" s="40"/>
+      <c r="A64" s="43"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:6">
-      <c r="A65" s="40"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:6">
-      <c r="A66" s="40"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:6">
-      <c r="A67" s="40"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
+      <c r="A67" s="43"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:6">
-      <c r="A68" s="40"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40" t="s">
-        <v>147</v>
+      <c r="A68" s="43"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" spans="1:6">
-      <c r="A69" s="40"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
+      <c r="A69" s="43"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="1:6">
-      <c r="A70" s="40"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="42"/>
-      <c r="D70" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
+      <c r="A70" s="43"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="E70" s="43"/>
+      <c r="F70" s="43"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="1:6">
-      <c r="A71" s="40"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="42"/>
-      <c r="D71" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
+      <c r="A71" s="43"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
     </row>
     <row r="72" ht="42" spans="1:6">
-      <c r="A72" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="B72" s="40"/>
-      <c r="C72" s="42"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="41" t="s">
-        <v>152</v>
+      <c r="A72" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="43"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="44" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" spans="1:6">
-      <c r="A73" s="40"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="42"/>
-      <c r="D73" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
+      <c r="A73" s="43"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="1:6">
-      <c r="A74" s="40"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="42"/>
-      <c r="D74" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
+      <c r="A74" s="43"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="43"/>
+      <c r="F74" s="43"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="1:6">
-      <c r="A75" s="40"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
+      <c r="A75" s="43"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="1:6">
-      <c r="A76" s="40"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="42"/>
-      <c r="D76" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
+      <c r="A76" s="43"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="E76" s="43"/>
+      <c r="F76" s="43"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="1:6">
-      <c r="A77" s="40"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
+      <c r="A77" s="43"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="1:6">
-      <c r="A78" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="B78" s="40"/>
-      <c r="C78" s="42"/>
-      <c r="D78" s="40" t="s">
-        <v>159</v>
-      </c>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
+      <c r="A78" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" s="43"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="E78" s="43"/>
+      <c r="F78" s="43"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="1:6">
-      <c r="A79" s="40"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="42"/>
-      <c r="D79" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
+      <c r="A79" s="43"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="E79" s="43"/>
+      <c r="F79" s="43"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="1:6">
-      <c r="A80" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="B80" s="40"/>
-      <c r="C80" s="42"/>
-      <c r="D80" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
+      <c r="A80" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="43"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="43"/>
+      <c r="F80" s="43"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="1:6">
-      <c r="A81" s="40"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="42"/>
-      <c r="D81" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
+      <c r="A81" s="43"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="E81" s="43"/>
+      <c r="F81" s="43"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="1:6">
-      <c r="A82" s="40"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="42"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40" t="s">
-        <v>164</v>
+      <c r="A82" s="43"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" spans="1:6">
-      <c r="A83" s="40"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="42"/>
-      <c r="D83" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
+      <c r="A83" s="43"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="45"/>
+      <c r="D83" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="E83" s="43"/>
+      <c r="F83" s="43"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="1:6">
-      <c r="A84" s="40"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="42"/>
-      <c r="D84" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-    </row>
-    <row r="85" ht="28" spans="1:6">
-      <c r="A85" s="40"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="42"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="41" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="45"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="D86" s="38"/>
-      <c r="E86" s="45"/>
-      <c r="F86" s="45"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="45"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D87" s="38"/>
-      <c r="E87" s="45"/>
-      <c r="F87" s="45"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="45"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="36"/>
-      <c r="D88" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E88" s="45"/>
-      <c r="F88" s="45"/>
+      <c r="A84" s="43"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="45"/>
+      <c r="D84" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E84" s="43"/>
+      <c r="F84" s="43"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="43"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="45"/>
+      <c r="D85" s="43"/>
+      <c r="E85" s="43"/>
+      <c r="F85" s="44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4">
+      <c r="C86" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="D86" s="41"/>
+    </row>
+    <row r="87" spans="3:4">
+      <c r="C87" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" s="41"/>
+    </row>
+    <row r="88" spans="3:4">
+      <c r="C88" s="39"/>
+      <c r="D88" s="41" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="89" spans="3:4">
-      <c r="C89" s="36"/>
-      <c r="D89" s="38"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="41"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="B90" s="38"/>
-      <c r="C90" s="36" t="s">
-        <v>172</v>
+      <c r="A90" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="41"/>
+      <c r="C90" s="39" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="47" t="s">
-        <v>173</v>
+      <c r="A91" s="43" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4867,800 +5048,799 @@
   <dimension ref="A1:F129"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="24.9153846153846" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.3461538461538" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.24615384615385" style="22" customWidth="1"/>
-    <col min="4" max="4" width="2.24615384615385" style="6" customWidth="1"/>
-    <col min="5" max="5" width="2.24615384615385" style="25" customWidth="1"/>
-    <col min="6" max="6" width="40.9538461538462" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="1" width="24.9153846153846" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.3461538461538" style="5" customWidth="1"/>
+    <col min="3" max="3" width="2.24615384615385" style="18" customWidth="1"/>
+    <col min="4" max="4" width="2.24615384615385" style="5" customWidth="1"/>
+    <col min="5" max="5" width="2.24615384615385" style="7" customWidth="1"/>
+    <col min="6" max="6" width="40.9538461538462" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="6" t="s">
-        <v>174</v>
+      <c r="B1" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>176</v>
+      <c r="B3" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="3:3">
-      <c r="C4" s="22" t="s">
-        <v>177</v>
+      <c r="C4" s="18" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="6" t="s">
-        <v>178</v>
+      <c r="D5" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>181</v>
+      <c r="A6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="6:6">
-      <c r="F7" s="26" t="s">
-        <v>182</v>
+      <c r="F7" s="28" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9" spans="4:4">
-      <c r="D9" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6">
+      <c r="F11" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="6:6">
-      <c r="F11" s="25" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="4:4">
-      <c r="D12" s="6" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="6" t="s">
-        <v>188</v>
+      <c r="D13" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="6:6">
-      <c r="F14" s="25" t="s">
-        <v>189</v>
+      <c r="F14" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="6:6">
-      <c r="F15" s="25" t="s">
-        <v>190</v>
+      <c r="F15" s="7" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>192</v>
+      <c r="A16" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="6:6">
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="18" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5" spans="2:6">
+      <c r="B26" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27" s="30"/>
+    </row>
+    <row r="28" ht="14.5" spans="2:4">
+      <c r="B28" s="29"/>
+      <c r="D28" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" ht="14.5" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5" spans="2:3">
+      <c r="B30" s="29"/>
+      <c r="C30" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" ht="14.5" spans="2:6">
+      <c r="B31" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" ht="14.5" spans="2:3">
+      <c r="B32" s="29"/>
+      <c r="C32" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6">
+      <c r="C34" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" ht="42" spans="1:6">
+      <c r="A37" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6">
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="4:6">
+      <c r="D40" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="4:6">
+      <c r="D41" s="5" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4">
-      <c r="D21" s="6" t="s">
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="4:4">
-      <c r="D22" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="6:6">
-      <c r="F23" s="25" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="22" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="4:4">
-      <c r="D25" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" spans="2:6">
-      <c r="B26" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="27" ht="14.5" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27" s="19"/>
-    </row>
-    <row r="28" ht="14.5" spans="2:4">
-      <c r="B28" s="27"/>
-      <c r="D28" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" ht="14.5" spans="1:3">
-      <c r="A29" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="22" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" spans="2:3">
-      <c r="B30" s="27"/>
-      <c r="C30" s="22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" ht="14.5" spans="2:6">
-      <c r="B31" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="32" ht="14.5" spans="2:3">
-      <c r="B32" s="27"/>
-      <c r="C32" s="22" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="3:6">
-      <c r="C34" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="25"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="D36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" ht="42" spans="1:6">
-      <c r="A37" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="39" spans="6:6">
-      <c r="F39" s="25"/>
-    </row>
-    <row r="40" spans="4:6">
-      <c r="D40" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F40" s="25"/>
-    </row>
-    <row r="41" spans="4:6">
-      <c r="D41" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F41" s="25"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="F42" s="25" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="F43" s="25" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="F44" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
     <row r="48" spans="3:3">
-      <c r="C48" s="22" t="s">
-        <v>231</v>
+      <c r="C48" s="18" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="3:3">
-      <c r="C49" s="22" t="s">
-        <v>232</v>
+      <c r="C49" s="18" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>178</v>
+      <c r="A50" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F51" s="25" t="s">
-        <v>235</v>
+      <c r="B51" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>237</v>
+      <c r="B52" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F53" s="25" t="s">
-        <v>240</v>
+      <c r="A53" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="2:4">
-      <c r="B54" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>242</v>
+      <c r="B54" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F55" s="25" t="s">
-        <v>245</v>
+      <c r="A55" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" s="6" t="s">
-        <v>246</v>
+      <c r="B56" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>248</v>
+      <c r="A57" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="6" t="s">
-        <v>249</v>
+      <c r="B58" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="59" spans="4:4">
-      <c r="D59" s="6" t="s">
-        <v>250</v>
+      <c r="D59" s="5" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="6:6">
-      <c r="F60" s="25" t="s">
-        <v>251</v>
+      <c r="F60" s="7" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>253</v>
+      <c r="A61" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>255</v>
+      <c r="B62" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="6:6">
-      <c r="F63" s="6" t="s">
-        <v>256</v>
+      <c r="F63" s="5" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="6:6">
-      <c r="F64" s="6" t="s">
-        <v>257</v>
+      <c r="F64" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="65" spans="6:6">
-      <c r="F65" s="26" t="s">
-        <v>258</v>
+      <c r="F65" s="28" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="4:4">
-      <c r="D66" s="6" t="s">
-        <v>188</v>
+      <c r="D66" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>260</v>
+      <c r="A67" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="3:3">
-      <c r="C69" s="22" t="s">
-        <v>261</v>
+      <c r="C69" s="18" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="4:4">
-      <c r="D70" s="6" t="s">
-        <v>178</v>
+      <c r="D70" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="F71" s="25" t="s">
-        <v>264</v>
+      <c r="A71" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F72" s="25" t="s">
-        <v>266</v>
+      <c r="A72" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="6:6">
-      <c r="F73" s="25" t="s">
-        <v>267</v>
+      <c r="F73" s="7" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>269</v>
+      <c r="A74" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="75" spans="4:4">
-      <c r="D75" s="6" t="s">
-        <v>270</v>
+      <c r="D75" s="5" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="4:6">
-      <c r="D76" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>271</v>
+      <c r="D76" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="4:4">
-      <c r="D78" s="6" t="s">
-        <v>188</v>
+      <c r="D78" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>195</v>
+      <c r="A79" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="83" spans="6:6">
+      <c r="F83" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="84" spans="6:6">
+      <c r="F84" s="33" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
+      <c r="B85" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" spans="4:6">
+      <c r="D92" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="83" spans="6:6">
-      <c r="F83" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="84" ht="14.5" spans="6:6">
-      <c r="F84" s="30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6">
-      <c r="B85" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D86" s="22" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C90" s="22" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="91" spans="4:4">
-      <c r="D91" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="92" spans="4:6">
-      <c r="D92" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="93" spans="4:4">
-      <c r="D93" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>290</v>
+      <c r="D94" s="5" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="3:3">
-      <c r="C95" s="22" t="s">
-        <v>291</v>
+      <c r="C95" s="18" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>293</v>
+      <c r="A96" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="97" spans="3:3">
-      <c r="C97" s="24" t="s">
-        <v>294</v>
+      <c r="C97" s="22" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="98" spans="3:4">
-      <c r="C98" s="24"/>
-      <c r="D98" s="14" t="s">
-        <v>295</v>
+      <c r="C98" s="22"/>
+      <c r="D98" s="13" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="3:6">
-      <c r="C99" s="24"/>
-      <c r="F99" s="25" t="s">
-        <v>296</v>
+      <c r="C99" s="22"/>
+      <c r="F99" s="7" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="100" spans="3:6">
-      <c r="C100" s="24"/>
-      <c r="D100" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="F100" s="25"/>
+      <c r="C100" s="22"/>
+      <c r="D100" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F100" s="7"/>
     </row>
     <row r="101" spans="3:6">
-      <c r="C101" s="24"/>
-      <c r="F101" s="25" t="s">
-        <v>298</v>
+      <c r="C101" s="22"/>
+      <c r="F101" s="7" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="102" spans="3:4">
-      <c r="C102" s="24"/>
-      <c r="D102" s="6" t="s">
-        <v>299</v>
+      <c r="C102" s="22"/>
+      <c r="D102" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="103" spans="3:3">
-      <c r="C103" s="24"/>
+      <c r="C103" s="22"/>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="31"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="32"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="33"/>
-      <c r="F104" s="31"/>
+      <c r="A104" s="34"/>
+      <c r="B104" s="34"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="34"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="34"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="31"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="32"/>
-      <c r="D105" s="31"/>
-      <c r="E105" s="33"/>
-      <c r="F105" s="31"/>
+      <c r="A105" s="34"/>
+      <c r="B105" s="34"/>
+      <c r="C105" s="35"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="34"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="31"/>
-      <c r="B106" s="31"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="33"/>
-      <c r="F106" s="31"/>
+      <c r="A106" s="34"/>
+      <c r="B106" s="34"/>
+      <c r="C106" s="35"/>
+      <c r="D106" s="34"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="34"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="31"/>
-      <c r="B107" s="31"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="31"/>
+      <c r="A107" s="34"/>
+      <c r="B107" s="34"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="34"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="31"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="32"/>
-      <c r="D108" s="31"/>
-      <c r="E108" s="33"/>
-      <c r="F108" s="31"/>
+      <c r="A108" s="34"/>
+      <c r="B108" s="34"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="34"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="31"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="32"/>
-      <c r="D109" s="31"/>
-      <c r="E109" s="33"/>
-      <c r="F109" s="31"/>
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="34"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="34"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="31"/>
-      <c r="B110" s="31"/>
-      <c r="C110" s="32"/>
-      <c r="D110" s="31"/>
-      <c r="E110" s="33"/>
-      <c r="F110" s="31"/>
+      <c r="A110" s="34"/>
+      <c r="B110" s="34"/>
+      <c r="C110" s="35"/>
+      <c r="D110" s="34"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="34"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="31"/>
-      <c r="B111" s="31"/>
-      <c r="C111" s="32"/>
-      <c r="D111" s="31"/>
-      <c r="E111" s="33"/>
-      <c r="F111" s="31"/>
+      <c r="A111" s="34"/>
+      <c r="B111" s="34"/>
+      <c r="C111" s="35"/>
+      <c r="D111" s="34"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="34"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="31"/>
-      <c r="B112" s="31"/>
-      <c r="C112" s="32"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="31"/>
+      <c r="A112" s="34"/>
+      <c r="B112" s="34"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="34"/>
     </row>
     <row r="123" spans="3:4">
-      <c r="C123" s="24"/>
-      <c r="D123" s="14"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="13"/>
     </row>
     <row r="124" spans="3:4">
-      <c r="C124" s="24"/>
-      <c r="D124" s="14"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="13"/>
     </row>
     <row r="125" spans="3:4">
-      <c r="C125" s="24"/>
-      <c r="D125" s="14"/>
+      <c r="C125" s="22"/>
+      <c r="D125" s="13"/>
     </row>
     <row r="126" spans="3:4">
-      <c r="C126" s="24"/>
-      <c r="D126" s="14"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="13"/>
     </row>
     <row r="127" spans="3:4">
-      <c r="C127" s="24"/>
-      <c r="D127" s="14"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="13"/>
     </row>
     <row r="128" spans="4:4">
-      <c r="D128" s="14"/>
+      <c r="D128" s="13"/>
     </row>
     <row r="129" spans="3:4">
-      <c r="C129" s="24"/>
-      <c r="D129" s="14"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5672,91 +5852,116 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="25.2538461538462" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="22" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="6" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="1" width="25.2538461538462" style="24" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="24" customWidth="1"/>
+    <col min="3" max="3" width="2.07692307692308" style="23" customWidth="1"/>
+    <col min="4" max="6" width="2.07692307692308" style="24" customWidth="1"/>
+    <col min="7" max="7" width="70.0769230769231" style="25" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="7:7">
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="G1" s="26"/>
+    </row>
+    <row r="2" s="23" customFormat="1" spans="1:7">
+      <c r="A2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="23"/>
+      <c r="E2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>301</v>
-      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>303</v>
+      <c r="A3" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>305</v>
+      <c r="B4" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>308</v>
+      <c r="B5" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>310</v>
+      <c r="A7" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="22" t="s">
+      <c r="A8" s="24" t="s">
         <v>314</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="24" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" ht="42" spans="7:7">
+      <c r="G15" s="25" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" ht="84" spans="7:7">
+      <c r="G16" s="25" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" ht="56" spans="6:7">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -5772,253 +5977,253 @@
   <dimension ref="A1:F59"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.46923076923077" style="22" customWidth="1"/>
-    <col min="4" max="5" width="2.46923076923077" style="6" customWidth="1"/>
-    <col min="6" max="6" width="64.4769230769231" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="1" width="25.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="5" customWidth="1"/>
+    <col min="3" max="3" width="2.46923076923077" style="18" customWidth="1"/>
+    <col min="4" max="5" width="2.46923076923077" style="5" customWidth="1"/>
+    <col min="6" max="6" width="64.4769230769231" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="22" customFormat="1" ht="13" customHeight="1" spans="2:2">
-      <c r="B1" s="22" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" s="22" customFormat="1" spans="1:5">
-      <c r="A2" s="22" t="s">
+    <row r="1" s="18" customFormat="1" ht="13" customHeight="1" spans="2:2">
+      <c r="B1" s="18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" s="18" customFormat="1" spans="1:5">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>318</v>
+      <c r="A3" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="6" t="s">
-        <v>319</v>
+      <c r="B4" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="6" t="s">
-        <v>320</v>
+      <c r="B5" s="5" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>322</v>
+      <c r="A6" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>324</v>
+      <c r="A8" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>326</v>
+      <c r="A9" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="4:4">
-      <c r="D10" s="6" t="s">
-        <v>327</v>
+      <c r="D10" s="5" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>329</v>
+      <c r="A11" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="4:4">
-      <c r="D12" s="6" t="s">
-        <v>330</v>
+      <c r="D12" s="5" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="5:5">
-      <c r="E13" s="6" t="s">
-        <v>331</v>
+      <c r="E13" s="5" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="3:3">
-      <c r="C14" s="22" t="s">
-        <v>332</v>
+      <c r="C14" s="18" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>334</v>
+      <c r="B15" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="16" ht="28" spans="6:6">
-      <c r="F16" s="23" t="s">
-        <v>335</v>
+      <c r="F16" s="21" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="17" ht="98" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>337</v>
+      <c r="A17" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="6:6">
-      <c r="F18" s="6" t="s">
-        <v>338</v>
+      <c r="F18" s="5" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>340</v>
+      <c r="A19" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="A23" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="F24" s="14"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="F25" s="14"/>
+      <c r="A25" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="F26" s="14"/>
+      <c r="A26" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="F26" s="13"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="A28" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="A29" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="A30" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" ht="15.5" spans="1:5">
       <c r="A31"/>
@@ -6028,163 +6233,163 @@
       <c r="E31"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>359</v>
+      <c r="A32" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>362</v>
+      <c r="A34" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>364</v>
+      <c r="A35" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>367</v>
+      <c r="A36" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="37" spans="5:5">
-      <c r="E37" s="6" t="s">
-        <v>368</v>
+      <c r="E37" s="5" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>371</v>
+      <c r="A38" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="6" t="s">
-        <v>372</v>
+      <c r="B39" s="5" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>374</v>
+      <c r="A41" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="4:4">
-      <c r="D42" s="6" t="s">
-        <v>375</v>
+      <c r="D42" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="4:4">
-      <c r="D43" s="6" t="s">
-        <v>376</v>
+      <c r="D43" s="5" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="44" spans="4:4">
-      <c r="D44" s="6" t="s">
-        <v>377</v>
+      <c r="D44" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="45" spans="4:4">
-      <c r="D45" s="6" t="s">
-        <v>378</v>
+      <c r="D45" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="46" spans="4:4">
-      <c r="D46" s="6" t="s">
-        <v>379</v>
+      <c r="D46" s="5" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="47" spans="4:4">
-      <c r="D47" s="6" t="s">
-        <v>380</v>
+      <c r="D47" s="5" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>382</v>
+      <c r="A48" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="49" ht="28" spans="6:6">
-      <c r="F49" s="23" t="s">
-        <v>383</v>
+      <c r="F49" s="21" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="50" spans="4:4">
-      <c r="D50" s="6" t="s">
-        <v>384</v>
+      <c r="D50" s="5" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="6" t="s">
-        <v>385</v>
+      <c r="D51" s="5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="4:4">
-      <c r="D52" s="6" t="s">
-        <v>386</v>
+      <c r="D52" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="53" spans="4:4">
-      <c r="D53" s="6" t="s">
-        <v>387</v>
+      <c r="D53" s="5" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="54" spans="4:4">
-      <c r="D54" s="6" t="s">
-        <v>388</v>
+      <c r="D54" s="5" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="55" spans="4:4">
-      <c r="D55" s="6" t="s">
-        <v>389</v>
+      <c r="D55" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="6" t="s">
-        <v>390</v>
+      <c r="D56" s="5" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="57" spans="4:4">
-      <c r="D57" s="6" t="s">
-        <v>391</v>
+      <c r="D57" s="5" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="4:4">
-      <c r="D58" s="6" t="s">
-        <v>392</v>
+      <c r="D58" s="5" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="59" spans="4:4">
-      <c r="D59" s="6" t="s">
-        <v>393</v>
+      <c r="D59" s="5" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -6199,654 +6404,654 @@
   <dimension ref="A1:F110"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.4153846153846" style="17" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="17" customWidth="1"/>
+    <col min="1" max="1" width="25.4153846153846" style="16" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="16" customWidth="1"/>
     <col min="3" max="3" width="2.07692307692308" style="20" customWidth="1"/>
-    <col min="4" max="4" width="3" style="17" customWidth="1"/>
-    <col min="5" max="5" width="2.38461538461538" style="17" customWidth="1"/>
-    <col min="6" max="6" width="48" style="17" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="17"/>
+    <col min="4" max="4" width="3" style="16" customWidth="1"/>
+    <col min="5" max="5" width="2.38461538461538" style="16" customWidth="1"/>
+    <col min="6" max="6" width="48" style="16" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="17" t="s">
-        <v>394</v>
+      <c r="B1" s="16" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="20" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="4:4">
-      <c r="D4" s="17" t="s">
-        <v>396</v>
+      <c r="D4" s="16" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="5" ht="42" spans="6:6">
-      <c r="F5" s="21" t="s">
-        <v>397</v>
+      <c r="F5" s="17" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1" spans="1:5">
-      <c r="A6" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
+      <c r="A6" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="16"/>
-      <c r="D7" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="E7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="3:5">
-      <c r="C8" s="16"/>
-      <c r="D8" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="E8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="3:5">
-      <c r="C9" s="16"/>
-      <c r="D9" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="E9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="3:5">
-      <c r="C10" s="16"/>
-      <c r="D10" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="E10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="16"/>
-      <c r="D11" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="E11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="4:4">
-      <c r="D12" s="17" t="s">
-        <v>405</v>
+      <c r="D12" s="16" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="15" t="s">
-        <v>406</v>
+      <c r="D13" s="14" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="4:4">
-      <c r="D14" s="15" t="s">
-        <v>407</v>
+      <c r="D14" s="14" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="4:4">
-      <c r="D15" s="6" t="s">
-        <v>331</v>
+      <c r="D15" s="5" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="4:4">
-      <c r="D16" s="6" t="s">
-        <v>408</v>
+      <c r="D16" s="5" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="6" t="s">
-        <v>409</v>
+      <c r="D17" s="5" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="4:4">
-      <c r="D18" s="6"/>
+      <c r="D18" s="5"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="17" t="s">
-        <v>410</v>
+      <c r="A19" s="16" t="s">
+        <v>419</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="17" t="s">
-        <v>412</v>
+      <c r="B20" s="16" t="s">
+        <v>421</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="17" t="s">
-        <v>414</v>
+      <c r="A21" s="16" t="s">
+        <v>423</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>417</v>
+      <c r="A22" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="17" t="s">
-        <v>418</v>
+      <c r="D23" s="16" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="4:4">
-      <c r="D24" s="17" t="s">
-        <v>419</v>
+      <c r="D24" s="16" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="4:4">
-      <c r="D25" s="17" t="s">
-        <v>420</v>
+      <c r="D25" s="16" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>422</v>
+      <c r="A26" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>424</v>
+      <c r="A27" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="17" t="s">
-        <v>425</v>
+      <c r="E28" s="16" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="4:4">
-      <c r="D29" s="17" t="s">
-        <v>426</v>
+      <c r="D29" s="16" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>429</v>
+      <c r="A30" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="20" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>434</v>
+      <c r="A32" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="4:5">
-      <c r="D33" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>436</v>
+      <c r="D33" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>440</v>
+      <c r="A34" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="D35" s="15"/>
+      <c r="C35" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="D35" s="14"/>
     </row>
     <row r="36" spans="3:4">
-      <c r="C36" s="16"/>
-      <c r="D36" s="15" t="s">
-        <v>442</v>
+      <c r="C36" s="15"/>
+      <c r="D36" s="14" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="3:4">
-      <c r="C37" s="16"/>
-      <c r="D37" s="15" t="s">
-        <v>443</v>
+      <c r="C37" s="15"/>
+      <c r="D37" s="14" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="3:4">
-      <c r="C38" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="D38" s="15"/>
+      <c r="C38" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="D38" s="14"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="16"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="14"/>
     </row>
     <row r="40" spans="3:4">
-      <c r="C40" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="D40" s="15"/>
+      <c r="C40" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="D40" s="14"/>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="16"/>
-      <c r="D41" s="15" t="s">
-        <v>446</v>
+      <c r="C41" s="15"/>
+      <c r="D41" s="14" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="17" t="s">
-        <v>447</v>
+      <c r="A43" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="44" spans="4:5">
-      <c r="D44" s="17" t="s">
-        <v>449</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>450</v>
+      <c r="D44" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="45" ht="28" spans="6:6">
-      <c r="F45" s="21" t="s">
-        <v>451</v>
+      <c r="F45" s="17" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="46" spans="6:6">
-      <c r="F46" s="21" t="s">
-        <v>452</v>
+      <c r="F46" s="17" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="47" spans="6:6">
-      <c r="F47" s="17" t="s">
-        <v>453</v>
+      <c r="F47" s="16" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="49" spans="5:5">
-      <c r="E49" s="17" t="s">
-        <v>454</v>
+      <c r="E49" s="16" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="17" t="s">
-        <v>455</v>
+      <c r="D51" s="16" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="5:5">
-      <c r="E52" s="17" t="s">
-        <v>456</v>
+      <c r="E52" s="16" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="53" spans="5:5">
-      <c r="E53" s="17" t="s">
-        <v>457</v>
+      <c r="E53" s="16" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="54" spans="5:5">
-      <c r="E54" s="17" t="s">
-        <v>458</v>
+      <c r="E54" s="16" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>460</v>
+      <c r="A55" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" s="20" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" spans="4:5">
-      <c r="D58" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>463</v>
+      <c r="D58" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="59" spans="5:5">
-      <c r="E59" s="17" t="s">
-        <v>464</v>
+      <c r="E59" s="16" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="60" spans="4:4">
-      <c r="D60" s="17" t="s">
-        <v>465</v>
+      <c r="D60" s="16" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>467</v>
+      <c r="A61" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>476</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="62" spans="2:4">
-      <c r="B62" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>470</v>
+      <c r="B62" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="17" t="s">
-        <v>471</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>472</v>
+      <c r="A63" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="20" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="65" spans="4:4">
-      <c r="D65" s="17" t="s">
-        <v>474</v>
+      <c r="D65" s="16" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" s="20" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" spans="2:4">
-      <c r="B67" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>477</v>
+      <c r="B67" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="17" t="s">
-        <v>478</v>
+      <c r="B68" s="16" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" s="20" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="70" spans="4:6">
-      <c r="D70" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>481</v>
+      <c r="D70" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="71" spans="5:5">
-      <c r="E71" s="17" t="s">
-        <v>482</v>
+      <c r="E71" s="16" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="17" t="s">
-        <v>483</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>485</v>
+      <c r="A72" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="73" spans="6:6">
-      <c r="F73" s="17" t="s">
-        <v>486</v>
+      <c r="F73" s="16" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="74" spans="6:6">
-      <c r="F74" s="17" t="s">
-        <v>487</v>
+      <c r="F74" s="16" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="75" spans="6:6">
-      <c r="F75" s="17" t="s">
-        <v>488</v>
+      <c r="F75" s="16" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>490</v>
+      <c r="A76" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="2:5">
-      <c r="B77" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>492</v>
+      <c r="B77" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="78" spans="5:5">
-      <c r="E78" s="17" t="s">
-        <v>493</v>
+      <c r="E78" s="16" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="79" spans="5:5">
-      <c r="E79" s="17" t="s">
-        <v>494</v>
+      <c r="E79" s="16" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="D81" s="17" t="s">
-        <v>497</v>
+      <c r="A81" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="17" t="s">
-        <v>498</v>
+      <c r="B83" s="16" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" s="20" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="17" t="s">
-        <v>500</v>
+      <c r="D86" s="16" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="17" t="s">
-        <v>501</v>
+      <c r="D87" s="16" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="17" t="s">
-        <v>502</v>
+      <c r="D88" s="16" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="89" spans="4:4">
-      <c r="D89" s="17" t="s">
-        <v>503</v>
+      <c r="D89" s="16" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="17" t="s">
-        <v>504</v>
+      <c r="A90" s="16" t="s">
+        <v>513</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="91" spans="2:4">
-      <c r="B91" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="D91" s="17" t="s">
-        <v>507</v>
+      <c r="B91" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="17" t="s">
-        <v>508</v>
+      <c r="A92" s="16" t="s">
+        <v>517</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
     </row>
     <row r="93" spans="4:4">
-      <c r="D93" s="17" t="s">
-        <v>510</v>
+      <c r="D93" s="16" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="94" spans="2:3">
-      <c r="B94" s="17" t="s">
-        <v>511</v>
+      <c r="B94" s="16" t="s">
+        <v>520</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" s="20" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="17" t="s">
-        <v>514</v>
+      <c r="A96" s="16" t="s">
+        <v>523</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="97" spans="4:4">
-      <c r="D97" s="17" t="s">
-        <v>516</v>
+      <c r="D97" s="16" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="98" spans="4:4">
-      <c r="D98" s="17" t="s">
-        <v>517</v>
+      <c r="D98" s="16" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="17" t="s">
-        <v>518</v>
+      <c r="A99" s="16" t="s">
+        <v>527</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="3:3">
       <c r="C100" s="20" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
     </row>
     <row r="101" spans="4:4">
-      <c r="D101" s="17" t="s">
-        <v>521</v>
+      <c r="D101" s="16" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="4:4">
-      <c r="D102" s="17" t="s">
-        <v>522</v>
+      <c r="D102" s="16" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="17" t="s">
-        <v>523</v>
+      <c r="A104" s="16" t="s">
+        <v>532</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
     </row>
     <row r="105" spans="4:4">
-      <c r="D105" s="17" t="s">
-        <v>525</v>
+      <c r="D105" s="16" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="4:4">
-      <c r="D106" s="17" t="s">
-        <v>526</v>
+      <c r="D106" s="16" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="17" t="s">
-        <v>527</v>
+      <c r="A107" s="16" t="s">
+        <v>536</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="110" spans="3:3">
       <c r="C110" s="20" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -6859,79 +7064,195 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H8"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.2538461538462" style="6" customWidth="1"/>
-    <col min="2" max="2" width="8.66923076923077" style="6"/>
-    <col min="3" max="3" width="5.66923076923077" style="6" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="6" customWidth="1"/>
-    <col min="6" max="6" width="23.4692307692308" style="6" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="1" width="17.2538461538462" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.66923076923077" style="5"/>
+    <col min="3" max="3" width="5.66923076923077" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="5" customWidth="1"/>
+    <col min="6" max="6" width="23.4692307692308" style="5" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="1" s="18" customFormat="1"/>
+    <row r="2" s="18" customFormat="1" spans="1:8">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>301</v>
+        <v>539</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="3:5">
-      <c r="C3" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>531</v>
+      <c r="C3" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="3:5">
-      <c r="C4" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>533</v>
+      <c r="C4" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="3:5">
-      <c r="C5" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>535</v>
+      <c r="C5" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="6" t="s">
-        <v>536</v>
+      <c r="C6" s="5" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>538</v>
+      <c r="C7" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="8" spans="6:6">
-      <c r="F8" s="6" t="s">
-        <v>539</v>
+      <c r="F8" s="5" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="5" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="5" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="5" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="5" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -6944,353 +7265,369 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:D46"/>
+  <dimension ref="A3:D49"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="8.66923076923077" style="13"/>
-    <col min="2" max="2" width="14.6923076923077" style="13" customWidth="1"/>
-    <col min="3" max="3" width="22.3846153846154" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="8.66923076923077" style="13"/>
+    <col min="1" max="1" width="8.66923076923077" style="12"/>
+    <col min="2" max="2" width="14.6923076923077" style="12" customWidth="1"/>
+    <col min="3" max="3" width="22.3846153846154" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="8.66923076923077" style="12"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:3">
-      <c r="C3" s="13" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3">
-      <c r="C5" s="13" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="13" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="8" ht="14" spans="4:4">
-      <c r="D8" s="14" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3">
-      <c r="C9" s="13" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="11" spans="3:3">
-      <c r="C11" s="13" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="13" ht="14" spans="1:4">
-      <c r="A13" s="15" t="s">
-        <v>546</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-    </row>
-    <row r="14" ht="14" spans="1:4">
-      <c r="A14" s="15" t="s">
-        <v>547</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-    </row>
-    <row r="15" ht="14" spans="1:4">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15" t="s">
-        <v>548</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>549</v>
-      </c>
-      <c r="D15" s="15"/>
+    <row r="3" spans="1:3">
+      <c r="A3" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="12" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="12" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="12" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="11" ht="14" spans="4:4">
+      <c r="D11" s="13" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="12" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="16" ht="14" spans="1:4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15" t="s">
-        <v>550</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D16" s="15"/>
+      <c r="A16" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" ht="14" spans="1:4">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16" t="s">
-        <v>552</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D17" s="15"/>
+      <c r="A17" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="18" ht="14" spans="1:4">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>555</v>
-      </c>
-      <c r="D18" s="15"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" ht="14" spans="1:4">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16" t="s">
-        <v>556</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>557</v>
-      </c>
-      <c r="D19" s="15"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" ht="14" spans="1:4">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15" t="s">
-        <v>558</v>
-      </c>
-      <c r="D20" s="15"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" ht="14" spans="1:4">
-      <c r="A21" s="15"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>560</v>
-      </c>
-      <c r="D21" s="15"/>
+        <v>592</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" ht="14" spans="1:4">
-      <c r="A22" s="15"/>
+      <c r="A22" s="14"/>
       <c r="B22" s="15" t="s">
-        <v>561</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>562</v>
-      </c>
-      <c r="D22" s="15"/>
+        <v>594</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" ht="14" spans="1:4">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16" t="s">
-        <v>563</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="D23" s="15"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="14" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" ht="14" spans="1:4">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="D24" s="15"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>598</v>
+      </c>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" ht="14" spans="1:4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="D25" s="15"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" ht="14" spans="1:4">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="D26" s="15"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>602</v>
+      </c>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" ht="14" spans="1:4">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="D27" s="15"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14" t="s">
+        <v>603</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" ht="14" spans="1:4">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="D28" s="15"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" ht="14" spans="1:4">
-      <c r="A29" s="15"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="D29" s="15"/>
+        <v>606</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="D29" s="14"/>
     </row>
     <row r="30" ht="14" spans="1:4">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="D30" s="15"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="D30" s="14"/>
     </row>
     <row r="31" ht="14" spans="1:4">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="D31" s="15"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" ht="14" spans="1:4">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="D32" s="15"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="D32" s="14"/>
     </row>
     <row r="33" ht="14" spans="1:4">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15" t="s">
-        <v>578</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="D33" s="15"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="D33" s="14"/>
     </row>
     <row r="34" ht="14" spans="1:4">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="D34" s="15"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="D34" s="14"/>
     </row>
     <row r="35" ht="14" spans="1:4">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="D35" s="15"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="D35" s="14"/>
     </row>
     <row r="36" ht="14" spans="1:4">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="D36" s="15"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14" t="s">
+        <v>616</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" ht="14" spans="1:4">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="D37" s="15"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="D37" s="14"/>
     </row>
     <row r="38" ht="14" spans="1:4">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="D38" s="15"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="D38" s="14"/>
     </row>
     <row r="39" ht="14" spans="1:4">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="D39" s="15"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="D39" s="14"/>
     </row>
     <row r="40" ht="14" spans="1:4">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="D40" s="15"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="D40" s="14"/>
     </row>
     <row r="41" ht="14" spans="1:4">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="D41" s="15"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="D41" s="14"/>
     </row>
     <row r="42" ht="14" spans="1:4">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="D42" s="15"/>
-    </row>
-    <row r="44" ht="14" spans="2:3">
-      <c r="B44" s="17" t="s">
-        <v>597</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="46" ht="14" spans="2:3">
-      <c r="B46" s="18" t="s">
-        <v>599</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>600</v>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="D42" s="14"/>
+    </row>
+    <row r="43" ht="14" spans="1:4">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="D43" s="14"/>
+    </row>
+    <row r="44" ht="14" spans="1:4">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="D44" s="14"/>
+    </row>
+    <row r="45" ht="14" spans="1:4">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="D45" s="14"/>
+    </row>
+    <row r="47" ht="14" spans="2:3">
+      <c r="B47" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="49" ht="14" spans="2:3">
+      <c r="B49" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -7305,353 +7642,353 @@
   <dimension ref="A1:C75"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="9.23076923076923" style="6"/>
+    <col min="1" max="16384" width="9.23076923076923" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="6" t="s">
-        <v>601</v>
+      <c r="A1" s="5" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>602</v>
+      <c r="A2" s="6" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8"/>
+      <c r="A3" s="7"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="9" t="s">
-        <v>603</v>
+      <c r="A4" s="8" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="10" t="s">
-        <v>604</v>
+      <c r="A6" s="9" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="10" t="s">
-        <v>605</v>
+      <c r="A7" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="11" t="s">
-        <v>606</v>
+      <c r="A8" s="10" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="11" t="s">
-        <v>607</v>
+      <c r="A9" s="10" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="11" t="s">
-        <v>608</v>
+      <c r="A10" s="10" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="10" t="s">
-        <v>609</v>
+      <c r="A11" s="9" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="7"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="9" t="s">
-        <v>610</v>
+      <c r="A13" s="8" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="8"/>
+      <c r="A14" s="7"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="10" t="s">
-        <v>611</v>
+      <c r="A15" s="9" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="10" t="s">
-        <v>605</v>
+      <c r="A16" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="11" t="s">
-        <v>612</v>
+      <c r="A17" s="10" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
-        <v>613</v>
+      <c r="A18" s="10" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
-        <v>614</v>
+      <c r="A19" s="10" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="10" t="s">
-        <v>615</v>
+      <c r="A20" s="9" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8"/>
+      <c r="A21" s="7"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
-        <v>616</v>
+      <c r="A22" s="8" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>618</v>
+      <c r="A23" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="6" t="s">
-        <v>619</v>
+      <c r="A24" s="7"/>
+      <c r="B24" s="5" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="10" t="s">
-        <v>620</v>
+      <c r="A25" s="9" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="10" t="s">
-        <v>605</v>
+      <c r="A26" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="11" t="s">
-        <v>621</v>
+      <c r="A27" s="10" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="11" t="s">
-        <v>622</v>
+      <c r="A28" s="10" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="11" t="s">
-        <v>623</v>
+      <c r="A29" s="10" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="10" t="s">
-        <v>624</v>
+      <c r="A30" s="9" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="8"/>
+      <c r="A31" s="7"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="9" t="s">
-        <v>625</v>
+      <c r="A32" s="8" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="8"/>
+      <c r="A33" s="7"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="10" t="s">
-        <v>626</v>
+      <c r="A34" s="9" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="10" t="s">
-        <v>605</v>
+      <c r="A35" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="11" t="s">
-        <v>627</v>
+      <c r="A36" s="10" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="11" t="s">
-        <v>628</v>
+      <c r="A37" s="10" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="11" t="s">
-        <v>629</v>
+      <c r="A38" s="10" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="10" t="s">
-        <v>630</v>
+      <c r="A39" s="9" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="8"/>
+      <c r="A40" s="7"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="9" t="s">
-        <v>631</v>
+      <c r="A41" s="8" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="8"/>
+      <c r="A42" s="7"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="10" t="s">
-        <v>632</v>
+      <c r="A43" s="9" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="10" t="s">
-        <v>605</v>
+      <c r="A44" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="11" t="s">
-        <v>633</v>
+      <c r="A45" s="10" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="11" t="s">
-        <v>634</v>
+      <c r="A46" s="10" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="11" t="s">
-        <v>635</v>
+      <c r="A47" s="10" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="10" t="s">
-        <v>636</v>
+      <c r="A48" s="9" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="8"/>
+      <c r="A49" s="7"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="9" t="s">
-        <v>637</v>
+      <c r="A50" s="8" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="8"/>
+      <c r="A51" s="7"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="10" t="s">
-        <v>638</v>
+      <c r="A52" s="9" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="10" t="s">
-        <v>605</v>
+      <c r="A53" s="9" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="11" t="s">
-        <v>639</v>
+      <c r="A54" s="10" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="11" t="s">
-        <v>640</v>
+      <c r="A55" s="10" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="11" t="s">
-        <v>641</v>
+      <c r="A56" s="10" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="10" t="s">
-        <v>642</v>
+      <c r="A57" s="9" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="8"/>
+      <c r="A58" s="7"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="7"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="9" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="9" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="8"/>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="10" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="11" t="s">
-        <v>645</v>
+      <c r="A63" s="10" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="11" t="s">
-        <v>646</v>
+      <c r="A64" s="10" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="11" t="s">
-        <v>647</v>
+      <c r="A65" s="10" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="10" t="s">
-        <v>648</v>
+      <c r="A66" s="9" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="8"/>
+      <c r="A67" s="7"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="9" t="s">
-        <v>649</v>
+      <c r="A68" s="8" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="7" t="s">
-        <v>650</v>
+      <c r="A69" s="6" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="6" t="s">
-        <v>651</v>
+      <c r="A70" s="5" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="6" t="s">
-        <v>652</v>
+      <c r="A71" s="5" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="12" t="s">
-        <v>653</v>
+      <c r="A73" s="11" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="6" t="s">
-        <v>654</v>
+      <c r="A74" s="5" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="6" t="s">
-        <v>655</v>
+      <c r="A75" s="5" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/p/py-25/py-core/topic-list_py.xlsx
+++ b/p/py-25/py-core/topic-list_py.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="880" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="21010" windowHeight="11150" tabRatio="880" firstSheet="3" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="701">
   <si>
     <t>Most basic things in py</t>
   </si>
@@ -968,6 +968,9 @@
   </si>
   <si>
     <t>len, del</t>
+  </si>
+  <si>
+    <t>count occurance of item in list: aList.count("me")</t>
   </si>
   <si>
     <t>aList.insert(0, "item at 0 index")</t>
@@ -3362,7 +3365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3413,9 +3416,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3430,12 +3430,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -4014,17 +4008,17 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="31" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D36" s="5" t="s">
@@ -4032,7 +4026,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="30" t="s">
         <v>47</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -4040,7 +4034,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="30" t="s">
         <v>49</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -4048,7 +4042,7 @@
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="31"/>
+      <c r="A39" s="30"/>
     </row>
     <row r="40" spans="3:3">
       <c r="C40" s="18" t="s">
@@ -4056,7 +4050,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -4072,7 +4066,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -4180,32 +4174,32 @@
     </row>
     <row r="12" ht="31" spans="5:5">
       <c r="E12" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="13" ht="31" spans="5:5">
       <c r="E13" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="15" ht="46.5" spans="5:5">
       <c r="E15" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" ht="62" spans="5:5">
       <c r="E16" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="18" ht="46.5" spans="5:5">
       <c r="E18" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="19" spans="5:5">
       <c r="E19" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -4220,816 +4214,816 @@
   <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="37" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="37" customWidth="1"/>
-    <col min="3" max="3" width="2.54615384615385" style="38" customWidth="1"/>
-    <col min="4" max="5" width="2.54615384615385" style="37" customWidth="1"/>
-    <col min="6" max="6" width="54.2384615384615" style="37" customWidth="1"/>
-    <col min="7" max="16384" width="8.66923076923077" style="37"/>
+    <col min="1" max="1" width="25.5" style="24" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="24" customWidth="1"/>
+    <col min="3" max="3" width="2.54615384615385" style="23" customWidth="1"/>
+    <col min="4" max="5" width="2.54615384615385" style="24" customWidth="1"/>
+    <col min="6" max="6" width="54.2384615384615" style="24" customWidth="1"/>
+    <col min="7" max="16384" width="8.66923076923077" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="4" spans="4:4">
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="36" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="36" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="37" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="39"/>
-      <c r="D12" s="42" t="s">
+      <c r="C12" s="36"/>
+      <c r="D12" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="41" t="s">
+      <c r="C13" s="36"/>
+      <c r="D13" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="41"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" spans="3:6">
-      <c r="C14" s="39"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41" t="s">
+      <c r="C14" s="36"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="24" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="16" spans="3:5">
-      <c r="C16" s="39"/>
-      <c r="D16" s="41" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="41"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="39"/>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="36"/>
+      <c r="D17" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="41"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="39"/>
-      <c r="D18" s="41" t="s">
+      <c r="C18" s="36"/>
+      <c r="D18" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="41"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="39"/>
-      <c r="D19" s="41" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="41"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="3:5">
-      <c r="C20" s="39"/>
-      <c r="D20" s="41" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="41"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="39"/>
-      <c r="D21" s="41" t="s">
+      <c r="C21" s="36"/>
+      <c r="D21" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="41"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="39"/>
-      <c r="D22" s="41" t="s">
+      <c r="C22" s="36"/>
+      <c r="D22" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="41"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="3:5">
-      <c r="C23" s="39"/>
-      <c r="D23" s="41" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="41"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="39"/>
-      <c r="D24" s="41" t="s">
+      <c r="C24" s="36"/>
+      <c r="D24" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="38"/>
     </row>
     <row r="25" spans="3:5">
-      <c r="C25" s="39"/>
-      <c r="D25" s="41" t="s">
+      <c r="C25" s="36"/>
+      <c r="D25" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="41"/>
+      <c r="E25" s="38"/>
     </row>
     <row r="26" spans="3:5">
-      <c r="C26" s="39"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27" spans="3:3">
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="36" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="28" spans="3:3">
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="36" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="39"/>
+      <c r="C29" s="36"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="1:5">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45" t="s">
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="1:6">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="1:6">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:6">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:6">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:6">
-      <c r="A35" s="43"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:6">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="41"/>
-      <c r="C36" s="39" t="s">
+      <c r="B36" s="38"/>
+      <c r="C36" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="43"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="40"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:6">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41" t="s">
+      <c r="A37" s="38"/>
+      <c r="B37" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="43"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="40"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:6">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="B38" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="43"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="40"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:6">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="B39" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="41" t="s">
+      <c r="C39" s="36"/>
+      <c r="D39" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="43"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="40"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:6">
-      <c r="A40" s="41"/>
-      <c r="B40" s="47" t="s">
+      <c r="A40" s="38"/>
+      <c r="B40" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="41" t="s">
+      <c r="C40" s="36"/>
+      <c r="D40" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="43"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="40"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:6">
-      <c r="A41" s="43"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="43" t="s">
+      <c r="A41" s="40"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43" t="s">
+      <c r="E41" s="40"/>
+      <c r="F41" s="40" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:6">
-      <c r="A42" s="43"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="45" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
     </row>
     <row r="43" ht="28" spans="1:6">
-      <c r="A43" s="43"/>
-      <c r="B43" s="43" t="s">
+      <c r="A43" s="40"/>
+      <c r="B43" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44" t="s">
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="41" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="44" ht="98" spans="1:6">
-      <c r="A44" s="43"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="45" t="s">
+      <c r="A44" s="40"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="44" t="s">
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="41" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" spans="1:6">
-      <c r="A45" s="43"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43" t="s">
+      <c r="A45" s="40"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" spans="1:6">
-      <c r="A46" s="43"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:6">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="43" t="s">
+      <c r="B47" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:6">
-      <c r="A48" s="43"/>
-      <c r="B48" s="43" t="s">
+      <c r="A48" s="40"/>
+      <c r="B48" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:6">
-      <c r="A49" s="43"/>
-      <c r="B49" s="43" t="s">
+      <c r="A49" s="40"/>
+      <c r="B49" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:6">
-      <c r="A50" s="43"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:6">
-      <c r="A51" s="43"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="45" t="s">
+      <c r="A51" s="40"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:6">
-      <c r="A52" s="43"/>
-      <c r="B52" s="43" t="s">
+      <c r="A52" s="40"/>
+      <c r="B52" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="43" t="s">
+      <c r="C52" s="42"/>
+      <c r="D52" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:6">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="43"/>
-      <c r="C53" s="45" t="s">
+      <c r="B53" s="40"/>
+      <c r="C53" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="1:6">
-      <c r="A54" s="43"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
+      <c r="A54" s="40"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="1:6">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="45" t="s">
+      <c r="B55" s="40"/>
+      <c r="C55" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="1:6">
-      <c r="A56" s="43"/>
-      <c r="B56" s="43"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="43" t="s">
+      <c r="A56" s="40"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="1:6">
-      <c r="A57" s="43"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="43" t="s">
+      <c r="A57" s="40"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:6">
-      <c r="A58" s="43"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43" t="s">
+      <c r="A58" s="40"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" spans="1:6">
-      <c r="A59" s="43"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="43" t="s">
+      <c r="A59" s="40"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="1:6">
-      <c r="A60" s="43" t="s">
+      <c r="A60" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="B60" s="43"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="43"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43" t="s">
+      <c r="B60" s="40"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" spans="1:6">
-      <c r="A61" s="43"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="43" t="s">
+      <c r="A61" s="40"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="1:6">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="B62" s="43"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43" t="s">
+      <c r="B62" s="40"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" spans="1:6">
-      <c r="A63" s="43"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="43" t="s">
+      <c r="A63" s="40"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="1:6">
-      <c r="A64" s="43"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="43" t="s">
+      <c r="A64" s="40"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="1:6">
-      <c r="A65" s="43"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="43" t="s">
+      <c r="A65" s="40"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="1:6">
-      <c r="A66" s="43"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="43" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="1:6">
-      <c r="A67" s="43"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="45"/>
-      <c r="D67" s="43" t="s">
+      <c r="A67" s="40"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="1:6">
-      <c r="A68" s="43"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43" t="s">
+      <c r="A68" s="40"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" spans="1:6">
-      <c r="A69" s="43"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="43" t="s">
+      <c r="A69" s="40"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="1:6">
-      <c r="A70" s="43"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="43" t="s">
+      <c r="A70" s="40"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="1:6">
-      <c r="A71" s="43"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="43" t="s">
+      <c r="A71" s="40"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
     </row>
     <row r="72" ht="42" spans="1:6">
-      <c r="A72" s="43" t="s">
+      <c r="A72" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="B72" s="43"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="44" t="s">
+      <c r="B72" s="40"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="41" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" spans="1:6">
-      <c r="A73" s="43"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="45"/>
-      <c r="D73" s="43" t="s">
+      <c r="A73" s="40"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="1:6">
-      <c r="A74" s="43"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="43" t="s">
+      <c r="A74" s="40"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="1:6">
-      <c r="A75" s="43"/>
-      <c r="B75" s="43"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="43" t="s">
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="1:6">
-      <c r="A76" s="43"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="43" t="s">
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="1:6">
-      <c r="A77" s="43"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="43" t="s">
+      <c r="A77" s="40"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="1:6">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="B78" s="43"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="43" t="s">
+      <c r="B78" s="40"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="1:6">
-      <c r="A79" s="43"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="43" t="s">
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="1:6">
-      <c r="A80" s="43" t="s">
+      <c r="A80" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="43"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="43" t="s">
+      <c r="B80" s="40"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="1:6">
-      <c r="A81" s="43"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="43" t="s">
+      <c r="A81" s="40"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="1:6">
-      <c r="A82" s="43"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="45"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43" t="s">
+      <c r="A82" s="40"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" spans="1:6">
-      <c r="A83" s="43"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="45"/>
-      <c r="D83" s="43" t="s">
+      <c r="A83" s="40"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="1:6">
-      <c r="A84" s="43"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="45"/>
-      <c r="D84" s="43" t="s">
+      <c r="A84" s="40"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="43"/>
-      <c r="B85" s="43"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="43"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="44" t="s">
+      <c r="A85" s="40"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="41" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="86" spans="3:4">
-      <c r="C86" s="39" t="s">
+      <c r="C86" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="D86" s="41"/>
+      <c r="D86" s="38"/>
     </row>
     <row r="87" spans="3:4">
-      <c r="C87" s="39" t="s">
+      <c r="C87" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="D87" s="41"/>
+      <c r="D87" s="38"/>
     </row>
     <row r="88" spans="3:4">
-      <c r="C88" s="39"/>
-      <c r="D88" s="41" t="s">
+      <c r="C88" s="36"/>
+      <c r="D88" s="38" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="89" spans="3:4">
-      <c r="C89" s="39"/>
-      <c r="D89" s="41"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="38"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="48" t="s">
+      <c r="A90" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="B90" s="41"/>
-      <c r="C90" s="39" t="s">
+      <c r="B90" s="38"/>
+      <c r="C90" s="36" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="43" t="s">
+      <c r="A91" s="40" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5045,7 +5039,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.9153846153846" style="5" customWidth="1"/>
@@ -5106,12 +5100,12 @@
       </c>
     </row>
     <row r="7" spans="6:6">
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>188</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -5219,7 +5213,7 @@
       </c>
     </row>
     <row r="26" ht="14.5" spans="2:6">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="28" t="s">
         <v>209</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -5233,14 +5227,14 @@
       <c r="A27" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B27" s="29"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="E27" s="30"/>
+      <c r="E27" s="29"/>
     </row>
     <row r="28" ht="14.5" spans="2:4">
-      <c r="B28" s="29"/>
+      <c r="B28" s="28"/>
       <c r="D28" s="5" t="s">
         <v>185</v>
       </c>
@@ -5249,19 +5243,19 @@
       <c r="A29" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B29" s="29"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="18" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="2:3">
-      <c r="B30" s="29"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="18" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="2:6">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="28" t="s">
         <v>216</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -5272,7 +5266,7 @@
       </c>
     </row>
     <row r="32" ht="14.5" spans="2:3">
-      <c r="B32" s="29"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="18" t="s">
         <v>218</v>
       </c>
@@ -5281,7 +5275,7 @@
       <c r="A33" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="30" t="s">
         <v>220</v>
       </c>
     </row>
@@ -5343,7 +5337,7 @@
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="31" t="s">
         <v>228</v>
       </c>
       <c r="F42" s="7" t="s">
@@ -5351,7 +5345,7 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="31" t="s">
         <v>228</v>
       </c>
       <c r="F43" s="7" t="s">
@@ -5359,7 +5353,7 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="31" t="s">
         <v>228</v>
       </c>
       <c r="F44" s="7" t="s">
@@ -5367,7 +5361,7 @@
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="31" t="s">
         <v>228</v>
       </c>
       <c r="F45" s="7" t="s">
@@ -5512,7 +5506,7 @@
       </c>
     </row>
     <row r="65" spans="6:6">
-      <c r="F65" s="28" t="s">
+      <c r="F65" s="27" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5559,42 +5553,39 @@
       </c>
     </row>
     <row r="73" spans="6:6">
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="6:6">
+      <c r="F74" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D74" s="5" t="s">
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="75" spans="4:4">
       <c r="D75" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="76" spans="4:6">
+    <row r="76" spans="4:4">
       <c r="D76" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="4:6">
+      <c r="D77" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F76" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="78" spans="4:4">
-      <c r="D78" s="5" t="s">
+      <c r="F77" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4">
+      <c r="D79" s="5" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -5602,222 +5593,226 @@
         <v>278</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="5" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="5" t="s">
+    <row r="82" spans="2:2">
+      <c r="B82" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D82" s="5" t="s">
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="83" spans="6:6">
-      <c r="F83" s="5" t="s">
+      <c r="D83" s="5" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="84" spans="6:6">
-      <c r="F84" s="33" t="s">
+      <c r="F84" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="2:6">
-      <c r="B85" s="5" t="s">
+    <row r="85" spans="6:6">
+      <c r="F85" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="F85" s="33" t="s">
+    </row>
+    <row r="86" spans="2:6">
+      <c r="B86" s="5" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="5" t="s">
+      <c r="F86" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D86" s="18" t="s">
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="5" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="5" t="s">
+      <c r="D87" s="18" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="5" t="s">
+    <row r="88" spans="1:1">
+      <c r="A88" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D89" s="5" t="s">
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="5" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="5" t="s">
+      <c r="D90" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C90" s="18" t="s">
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="5" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="91" spans="4:4">
-      <c r="D91" s="5" t="s">
+      <c r="C91" s="18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="92" spans="4:6">
-      <c r="D92" s="5" t="s">
+    <row r="93" spans="4:6">
+      <c r="D93" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F92" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="93" spans="4:4">
-      <c r="D93" s="5" t="s">
+      <c r="F93" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="95" spans="3:3">
-      <c r="C95" s="18" t="s">
+    <row r="95" spans="1:4">
+      <c r="A95" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D95" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="5" t="s">
+    <row r="96" spans="3:3">
+      <c r="C96" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="D96" s="5" t="s">
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="5" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="97" spans="3:3">
-      <c r="C97" s="22" t="s">
+      <c r="D97" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="98" spans="3:4">
-      <c r="C98" s="22"/>
-      <c r="D98" s="13" t="s">
+    <row r="98" spans="3:3">
+      <c r="C98" s="22" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="3:6">
+    <row r="99" spans="3:4">
       <c r="C99" s="22"/>
-      <c r="F99" s="7" t="s">
+      <c r="D99" s="13" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="100" spans="3:6">
       <c r="C100" s="22"/>
-      <c r="D100" s="5" t="s">
+      <c r="F100" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F100" s="7"/>
     </row>
     <row r="101" spans="3:6">
       <c r="C101" s="22"/>
-      <c r="F101" s="7" t="s">
+      <c r="D101" s="5" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="102" spans="3:4">
+      <c r="F101" s="7"/>
+    </row>
+    <row r="102" spans="3:6">
       <c r="C102" s="22"/>
-      <c r="D102" s="5" t="s">
+      <c r="F102" s="7" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="103" spans="3:3">
+    <row r="103" spans="3:4">
       <c r="C103" s="22"/>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" s="34"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="34"/>
-      <c r="E104" s="36"/>
-      <c r="F104" s="34"/>
+      <c r="D103" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3">
+      <c r="C104" s="22"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="34"/>
-      <c r="B105" s="34"/>
-      <c r="C105" s="35"/>
-      <c r="D105" s="34"/>
-      <c r="E105" s="36"/>
-      <c r="F105" s="34"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="33"/>
+      <c r="C105" s="34"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="35"/>
+      <c r="F105" s="33"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="35"/>
-      <c r="D106" s="34"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="34"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="33"/>
+      <c r="C106" s="34"/>
+      <c r="D106" s="33"/>
+      <c r="E106" s="35"/>
+      <c r="F106" s="33"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="34"/>
-      <c r="B107" s="34"/>
-      <c r="C107" s="35"/>
-      <c r="D107" s="34"/>
-      <c r="E107" s="36"/>
-      <c r="F107" s="34"/>
+      <c r="A107" s="33"/>
+      <c r="B107" s="33"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="35"/>
+      <c r="F107" s="33"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="34"/>
-      <c r="B108" s="34"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="34"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="33"/>
+      <c r="C108" s="34"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="35"/>
+      <c r="F108" s="33"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="34"/>
-      <c r="B109" s="34"/>
-      <c r="C109" s="35"/>
-      <c r="D109" s="34"/>
-      <c r="E109" s="36"/>
-      <c r="F109" s="34"/>
+      <c r="A109" s="33"/>
+      <c r="B109" s="33"/>
+      <c r="C109" s="34"/>
+      <c r="D109" s="33"/>
+      <c r="E109" s="35"/>
+      <c r="F109" s="33"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="34"/>
-      <c r="B110" s="34"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="34"/>
-      <c r="E110" s="36"/>
-      <c r="F110" s="34"/>
+      <c r="A110" s="33"/>
+      <c r="B110" s="33"/>
+      <c r="C110" s="34"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="35"/>
+      <c r="F110" s="33"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="34"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="35"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="34"/>
+      <c r="A111" s="33"/>
+      <c r="B111" s="33"/>
+      <c r="C111" s="34"/>
+      <c r="D111" s="33"/>
+      <c r="E111" s="35"/>
+      <c r="F111" s="33"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="34"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="35"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="36"/>
-      <c r="F112" s="34"/>
-    </row>
-    <row r="123" spans="3:4">
-      <c r="C123" s="22"/>
-      <c r="D123" s="13"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="34"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="33"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="33"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="35"/>
+      <c r="F113" s="33"/>
     </row>
     <row r="124" spans="3:4">
       <c r="C124" s="22"/>
@@ -5835,12 +5830,16 @@
       <c r="C127" s="22"/>
       <c r="D127" s="13"/>
     </row>
-    <row r="128" spans="4:4">
+    <row r="128" spans="3:4">
+      <c r="C128" s="22"/>
       <c r="D128" s="13"/>
     </row>
-    <row r="129" spans="3:4">
-      <c r="C129" s="22"/>
+    <row r="129" spans="4:4">
       <c r="D129" s="13"/>
+    </row>
+    <row r="130" spans="3:4">
+      <c r="C130" s="22"/>
+      <c r="D130" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5852,7 +5851,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A2:G17"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="25.2538461538462" style="24" customWidth="1"/>
@@ -5864,9 +5863,6 @@
     <col min="9" max="16384" width="8.66923076923077" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:7">
-      <c r="G1" s="26"/>
-    </row>
     <row r="2" s="23" customFormat="1" spans="1:7">
       <c r="A2" s="23" t="s">
         <v>1</v>
@@ -5877,91 +5873,89 @@
       <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23"/>
       <c r="E2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" ht="42" spans="7:7">
       <c r="G15" s="25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" ht="84" spans="7:7">
       <c r="G16" s="25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" ht="56" spans="6:7">
       <c r="F17" s="25"/>
       <c r="G17" s="25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +5981,7 @@
   <sheetData>
     <row r="1" s="18" customFormat="1" ht="13" customHeight="1" spans="2:2">
       <c r="B1" s="18" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" s="18" customFormat="1" spans="1:5">
@@ -6006,116 +6000,116 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" ht="28" spans="6:6">
       <c r="F16" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" ht="98" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="6:6">
       <c r="F18" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -6126,19 +6120,19 @@
       <c r="B22" s="13"/>
       <c r="C22" s="22"/>
       <c r="D22" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="22"/>
       <c r="D23" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
@@ -6149,33 +6143,33 @@
       <c r="C24" s="22"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="22"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F26" s="13"/>
     </row>
@@ -6184,29 +6178,29 @@
       <c r="B27" s="13"/>
       <c r="C27" s="22"/>
       <c r="D27" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="22"/>
       <c r="D28" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="13"/>
@@ -6215,10 +6209,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C30" s="22"/>
       <c r="D30" s="13"/>
@@ -6234,162 +6228,162 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="37" spans="5:5">
       <c r="E37" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="4:4">
       <c r="D42" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="4:4">
       <c r="D43" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" spans="4:4">
       <c r="D44" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="4:4">
       <c r="D46" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" ht="28" spans="6:6">
       <c r="F49" s="21" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6415,7 +6409,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="2:5">
@@ -6431,25 +6425,25 @@
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" ht="42" spans="6:6">
       <c r="F5" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -6457,66 +6451,66 @@
     <row r="7" spans="3:5">
       <c r="C7" s="15"/>
       <c r="D7" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" spans="3:5">
       <c r="C8" s="15"/>
       <c r="D8" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E8" s="14"/>
     </row>
     <row r="9" spans="3:5">
       <c r="C9" s="15"/>
       <c r="D9" s="16" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E9" s="14"/>
     </row>
     <row r="10" spans="3:5">
       <c r="C10" s="15"/>
       <c r="D10" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E10" s="14"/>
     </row>
     <row r="11" spans="3:5">
       <c r="C11" s="15"/>
       <c r="D11" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E11" s="14"/>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -6524,150 +6518,150 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" s="16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" s="16" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" s="16" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" s="15"/>
       <c r="D36" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" s="15"/>
       <c r="D37" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D38" s="14"/>
     </row>
@@ -6677,381 +6671,381 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="15"/>
       <c r="D41" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="16" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" ht="28" spans="6:6">
       <c r="F45" s="17" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="46" spans="6:6">
       <c r="F46" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" s="16" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="16" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="16" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="52" spans="5:5">
       <c r="E52" s="16" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="16" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="5:5">
       <c r="E54" s="16" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="16" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" s="20" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="58" spans="4:5">
       <c r="D58" s="16" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59" spans="5:5">
       <c r="E59" s="16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="16" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" s="20" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="16" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" s="20" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="16" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" s="20" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="70" spans="4:6">
       <c r="D70" s="16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="71" spans="5:5">
       <c r="E71" s="16" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="73" spans="6:6">
       <c r="F73" s="16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="74" spans="6:6">
       <c r="F74" s="16" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="75" spans="6:6">
       <c r="F75" s="16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="16" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="78" spans="5:5">
       <c r="E78" s="16" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="5:5">
       <c r="E79" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" s="20" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="86" spans="4:4">
       <c r="D86" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" s="16" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" s="16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="89" spans="4:4">
       <c r="D89" s="16" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="B91" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" s="16" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="B94" s="16" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" s="20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="97" spans="4:4">
       <c r="D97" s="16" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="98" spans="4:4">
       <c r="D98" s="16" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="16" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="3:3">
       <c r="C100" s="20" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101" spans="4:4">
       <c r="D101" s="16" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="102" spans="4:4">
       <c r="D102" s="16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="105" spans="4:4">
       <c r="D105" s="16" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="106" spans="4:4">
       <c r="D106" s="16" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="16" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="110" spans="3:3">
       <c r="C110" s="20" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -7092,167 +7086,167 @@
         <v>4</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="3:5">
       <c r="C3" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="3:5">
       <c r="C4" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="3:5">
       <c r="C5" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="3:5">
       <c r="C7" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="6:6">
       <c r="F8" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="32" spans="3:3">
       <c r="C32" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -7276,53 +7270,53 @@
   <sheetData>
     <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" ht="14" spans="4:4">
       <c r="D11" s="13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16" ht="14" spans="1:4">
       <c r="A16" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -7330,7 +7324,7 @@
     </row>
     <row r="17" ht="14" spans="1:4">
       <c r="A17" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -7339,50 +7333,50 @@
     <row r="18" ht="14" spans="1:4">
       <c r="A18" s="14"/>
       <c r="B18" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D18" s="14"/>
     </row>
     <row r="19" ht="14" spans="1:4">
       <c r="A19" s="14"/>
       <c r="B19" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D19" s="14"/>
     </row>
     <row r="20" ht="14" spans="1:4">
       <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D20" s="14"/>
     </row>
     <row r="21" ht="14" spans="1:4">
       <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D21" s="14"/>
     </row>
     <row r="22" ht="14" spans="1:4">
       <c r="A22" s="14"/>
       <c r="B22" s="15" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D22" s="14"/>
     </row>
@@ -7390,244 +7384,244 @@
       <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="14" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D23" s="14"/>
     </row>
     <row r="24" ht="14" spans="1:4">
       <c r="A24" s="14"/>
       <c r="B24" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D24" s="14"/>
     </row>
     <row r="25" ht="14" spans="1:4">
       <c r="A25" s="14"/>
       <c r="B25" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D25" s="14"/>
     </row>
     <row r="26" ht="14" spans="1:4">
       <c r="A26" s="14"/>
       <c r="B26" s="15" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D26" s="14"/>
     </row>
     <row r="27" ht="14" spans="1:4">
       <c r="A27" s="14"/>
       <c r="B27" s="14" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D27" s="14"/>
     </row>
     <row r="28" ht="14" spans="1:4">
       <c r="A28" s="14"/>
       <c r="B28" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>605</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>604</v>
       </c>
       <c r="D28" s="14"/>
     </row>
     <row r="29" ht="14" spans="1:4">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D29" s="14"/>
     </row>
     <row r="30" ht="14" spans="1:4">
       <c r="A30" s="14"/>
       <c r="B30" s="14" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D30" s="14"/>
     </row>
     <row r="31" ht="14" spans="1:4">
       <c r="A31" s="14"/>
       <c r="B31" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>608</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>607</v>
       </c>
       <c r="D31" s="14"/>
     </row>
     <row r="32" ht="14" spans="1:4">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D32" s="14"/>
     </row>
     <row r="33" ht="14" spans="1:4">
       <c r="A33" s="14"/>
       <c r="B33" s="14" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D33" s="14"/>
     </row>
     <row r="34" ht="14" spans="1:4">
       <c r="A34" s="14"/>
       <c r="B34" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D34" s="14"/>
     </row>
     <row r="35" ht="14" spans="1:4">
       <c r="A35" s="14"/>
       <c r="B35" s="14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D35" s="14"/>
     </row>
     <row r="36" ht="14" spans="1:4">
       <c r="A36" s="14"/>
       <c r="B36" s="14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D36" s="14"/>
     </row>
     <row r="37" ht="14" spans="1:4">
       <c r="A37" s="14"/>
       <c r="B37" s="14" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D37" s="14"/>
     </row>
     <row r="38" ht="14" spans="1:4">
       <c r="A38" s="14"/>
       <c r="B38" s="14" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D38" s="14"/>
     </row>
     <row r="39" ht="14" spans="1:4">
       <c r="A39" s="14"/>
       <c r="B39" s="14" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D39" s="14"/>
     </row>
     <row r="40" ht="14" spans="1:4">
       <c r="A40" s="14"/>
       <c r="B40" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D40" s="14"/>
     </row>
     <row r="41" ht="14" spans="1:4">
       <c r="A41" s="14"/>
       <c r="B41" s="14" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D41" s="14"/>
     </row>
     <row r="42" ht="14" spans="1:4">
       <c r="A42" s="14"/>
       <c r="B42" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D42" s="14"/>
     </row>
     <row r="43" ht="14" spans="1:4">
       <c r="A43" s="14"/>
       <c r="B43" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D43" s="14"/>
     </row>
     <row r="44" ht="14" spans="1:4">
       <c r="A44" s="14"/>
       <c r="B44" s="14" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D44" s="14"/>
     </row>
     <row r="45" ht="14" spans="1:4">
       <c r="A45" s="14"/>
       <c r="B45" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D45" s="14"/>
     </row>
     <row r="47" ht="14" spans="2:3">
       <c r="B47" s="16" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="49" ht="14" spans="2:3">
       <c r="B49" s="17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -7647,12 +7641,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7660,7 +7654,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -7668,32 +7662,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -7701,7 +7695,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -7709,32 +7703,32 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="10" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7742,51 +7736,51 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="7"/>
       <c r="B24" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="10" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -7794,7 +7788,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -7802,32 +7796,32 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -7835,7 +7829,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="8" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -7843,32 +7837,32 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -7876,7 +7870,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -7884,32 +7878,32 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -7917,7 +7911,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -7925,32 +7919,32 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="10" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="10" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -7958,37 +7952,37 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
